--- a/DCE 2-1/Regular Assessment DCE 2-1.xlsx
+++ b/DCE 2-1/Regular Assessment DCE 2-1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Attendance\DCE 2-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\DCE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80454351-31A5-4AEE-A3E8-338FE11F981A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F984B06E-4EDD-4DCD-9D2A-22C698BC4B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="55">
   <si>
     <t>SL</t>
   </si>
@@ -200,10 +200,10 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Knitting Action</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>Knitting Action (Latch)</t>
+  </si>
+  <si>
+    <t>Knitting Action (Bearded)</t>
   </si>
 </sst>
 </file>
@@ -397,9 +397,6 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -410,6 +407,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -725,14 +725,15 @@
     <col min="5" max="5" width="32.21875" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="32.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="20.77734375" style="7"/>
+    <col min="9" max="9" width="30.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="20.77734375" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="18"/>
       <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
@@ -875,7 +876,9 @@
       <c r="H3" s="13">
         <v>46266</v>
       </c>
-      <c r="I3" s="13"/>
+      <c r="I3" s="13">
+        <v>46272</v>
+      </c>
       <c r="J3" s="13"/>
       <c r="K3" s="13"/>
       <c r="L3" s="13"/>
@@ -904,7 +907,7 @@
       </c>
       <c r="D4" s="15">
         <f>COUNTIF(E4:X4,"P")/(COUNTIF(E4:X4,"P")+COUNTIF(E4:X4,"A"))</f>
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>45</v>
@@ -918,7 +921,9 @@
       <c r="H4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I4" s="1"/>
+      <c r="I4" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -948,7 +953,7 @@
       </c>
       <c r="D5" s="15">
         <f t="shared" ref="D5:D41" si="2">COUNTIF(E5:X5,"P")/(COUNTIF(E5:X5,"P")+COUNTIF(E5:X5,"A"))</f>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>45</v>
@@ -962,7 +967,9 @@
       <c r="H5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1006,7 +1013,9 @@
       <c r="H6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1050,7 +1059,9 @@
       <c r="H7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1080,7 +1091,7 @@
       </c>
       <c r="D8" s="15">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>45</v>
@@ -1094,7 +1105,9 @@
       <c r="H8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1124,7 +1137,7 @@
       </c>
       <c r="D9" s="15">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>45</v>
@@ -1138,7 +1151,9 @@
       <c r="H9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -1168,7 +1183,7 @@
       </c>
       <c r="D10" s="15">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>45</v>
@@ -1182,7 +1197,9 @@
       <c r="H10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I10" s="1"/>
+      <c r="I10" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -1212,7 +1229,7 @@
       </c>
       <c r="D11" s="15">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>45</v>
@@ -1226,7 +1243,9 @@
       <c r="H11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -1270,7 +1289,9 @@
       <c r="H12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -1314,7 +1335,9 @@
       <c r="H13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -1358,7 +1381,9 @@
       <c r="H14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -1402,7 +1427,9 @@
       <c r="H15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I15" s="1"/>
+      <c r="I15" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -1446,7 +1473,9 @@
       <c r="H16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I16" s="1"/>
+      <c r="I16" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -1490,7 +1519,9 @@
       <c r="H17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I17" s="1"/>
+      <c r="I17" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1520,7 +1551,7 @@
       </c>
       <c r="D18" s="15">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>45</v>
@@ -1534,7 +1565,9 @@
       <c r="H18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I18" s="1"/>
+      <c r="I18" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -1564,7 +1597,7 @@
       </c>
       <c r="D19" s="15">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>45</v>
@@ -1578,7 +1611,9 @@
       <c r="H19" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I19" s="1"/>
+      <c r="I19" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -1608,7 +1643,7 @@
       </c>
       <c r="D20" s="15">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>45</v>
@@ -1622,7 +1657,9 @@
       <c r="H20" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I20" s="1"/>
+      <c r="I20" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -1652,7 +1689,7 @@
       </c>
       <c r="D21" s="15">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>43</v>
@@ -1666,7 +1703,9 @@
       <c r="H21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I21" s="1"/>
+      <c r="I21" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -1710,7 +1749,9 @@
       <c r="H22" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I22" s="1"/>
+      <c r="I22" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -1754,7 +1795,9 @@
       <c r="H23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I23" s="1"/>
+      <c r="I23" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -1784,7 +1827,7 @@
       </c>
       <c r="D24" s="15">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>45</v>
@@ -1798,7 +1841,9 @@
       <c r="H24" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I24" s="1"/>
+      <c r="I24" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -1828,7 +1873,7 @@
       </c>
       <c r="D25" s="15">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>43</v>
@@ -1842,7 +1887,9 @@
       <c r="H25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I25" s="1"/>
+      <c r="I25" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1886,7 +1933,9 @@
       <c r="H26" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I26" s="1"/>
+      <c r="I26" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -1916,7 +1965,7 @@
       </c>
       <c r="D27" s="15">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>43</v>
@@ -1930,7 +1979,9 @@
       <c r="H27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I27" s="1"/>
+      <c r="I27" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1974,7 +2025,9 @@
       <c r="H28" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I28" s="1"/>
+      <c r="I28" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -2018,7 +2071,9 @@
       <c r="H29" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I29" s="1"/>
+      <c r="I29" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -2048,7 +2103,7 @@
       </c>
       <c r="D30" s="15">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>45</v>
@@ -2062,7 +2117,9 @@
       <c r="H30" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I30" s="1"/>
+      <c r="I30" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -2106,7 +2163,9 @@
       <c r="H31" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I31" s="1"/>
+      <c r="I31" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -2150,7 +2209,9 @@
       <c r="H32" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I32" s="1"/>
+      <c r="I32" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -2194,7 +2255,9 @@
       <c r="H33" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I33" s="1"/>
+      <c r="I33" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -2238,7 +2301,9 @@
       <c r="H34" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I34" s="1"/>
+      <c r="I34" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -2282,7 +2347,9 @@
       <c r="H35" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I35" s="1"/>
+      <c r="I35" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -2326,7 +2393,9 @@
       <c r="H36" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I36" s="1"/>
+      <c r="I36" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -2370,7 +2439,9 @@
       <c r="H37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I37" s="1"/>
+      <c r="I37" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -2400,7 +2471,7 @@
       </c>
       <c r="D38" s="15">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>43</v>
@@ -2414,7 +2485,9 @@
       <c r="H38" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I38" s="1"/>
+      <c r="I38" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -2458,7 +2531,9 @@
       <c r="H39" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I39" s="1"/>
+      <c r="I39" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -2488,7 +2563,7 @@
       </c>
       <c r="D40" s="15">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>45</v>
@@ -2502,7 +2577,9 @@
       <c r="H40" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I40" s="1"/>
+      <c r="I40" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -2532,7 +2609,7 @@
       </c>
       <c r="D41" s="15">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>45</v>
@@ -2546,7 +2623,9 @@
       <c r="H41" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I41" s="1"/>
+      <c r="I41" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -2603,18 +2682,19 @@
     <col min="1" max="1" width="8.109375" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.109375" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="15.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15.44140625" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="3.44140625" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="4.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="20.77734375" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="18"/>
       <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
@@ -2630,10 +2710,10 @@
       <c r="G1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="20"/>
+      <c r="I1" s="19"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -2649,11 +2729,13 @@
       <c r="D2" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="12"/>
+      <c r="E2" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
     </row>
     <row r="3" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -2665,22 +2747,22 @@
       <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="17">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17">
+      <c r="D3" s="20">
+        <v>7.5</v>
+      </c>
+      <c r="E3" s="20">
+        <v>7.5</v>
+      </c>
+      <c r="F3" s="20">
+        <v>7.5</v>
+      </c>
+      <c r="G3" s="20">
+        <v>7.5</v>
+      </c>
+      <c r="H3" s="16">
+        <v>30</v>
+      </c>
+      <c r="I3" s="16">
         <v>7.5</v>
       </c>
     </row>
@@ -2694,15 +2776,15 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17">
         <f>SUM(D4:G4)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="17">
         <f>(H4/20)*7.5</f>
         <v>0</v>
       </c>
@@ -2718,15 +2800,15 @@
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18">
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17">
         <f t="shared" ref="H5:H41" si="1">SUM(D5:G5)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="17">
         <f t="shared" ref="I5:I41" si="2">(H5/20)*7.5</f>
         <v>0</v>
       </c>
@@ -2742,15 +2824,15 @@
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="18">
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2766,15 +2848,15 @@
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="18">
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2790,15 +2872,15 @@
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="18">
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2814,15 +2896,15 @@
       <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="18">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2838,15 +2920,15 @@
       <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="18">
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2862,15 +2944,15 @@
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="18">
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2886,15 +2968,15 @@
       <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="18">
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2910,15 +2992,15 @@
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="18">
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2934,15 +3016,15 @@
       <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="18">
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2958,15 +3040,15 @@
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="18">
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2982,15 +3064,15 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="18">
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3006,15 +3088,15 @@
       <c r="C17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="18">
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3030,15 +3112,15 @@
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="18">
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3054,15 +3136,15 @@
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="18">
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3078,15 +3160,15 @@
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="18">
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3102,15 +3184,15 @@
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="18">
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3126,15 +3208,15 @@
       <c r="C22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="18">
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3150,15 +3232,15 @@
       <c r="C23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="18">
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3174,15 +3256,15 @@
       <c r="C24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="18">
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3198,15 +3280,15 @@
       <c r="C25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="18">
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3222,15 +3304,15 @@
       <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="18">
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3246,15 +3328,15 @@
       <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="18">
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3270,15 +3352,15 @@
       <c r="C28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="18">
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3294,15 +3376,15 @@
       <c r="C29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="18">
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3318,15 +3400,15 @@
       <c r="C30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="18">
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3342,15 +3424,15 @@
       <c r="C31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="18">
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3370,11 +3452,11 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="18">
+      <c r="H32" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3394,11 +3476,11 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-      <c r="H33" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="18">
+      <c r="H33" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3418,11 +3500,11 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="18">
+      <c r="H34" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3442,11 +3524,11 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="H35" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="18">
+      <c r="H35" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3466,11 +3548,11 @@
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="18">
+      <c r="H36" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3490,11 +3572,11 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="18">
+      <c r="H37" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3514,11 +3596,11 @@
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
-      <c r="H38" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="18">
+      <c r="H38" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3538,11 +3620,11 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-      <c r="H39" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="18">
+      <c r="H39" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3562,11 +3644,11 @@
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="H40" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I40" s="18">
+      <c r="H40" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I40" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3586,11 +3668,11 @@
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-      <c r="H41" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I41" s="18">
+      <c r="H41" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I41" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3603,8 +3685,5 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="D3:G3" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/DCE 2-1/Regular Assessment DCE 2-1.xlsx
+++ b/DCE 2-1/Regular Assessment DCE 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\DCE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F984B06E-4EDD-4DCD-9D2A-22C698BC4B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01103466-D657-41EA-AF83-A39594AC875E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="55">
   <si>
     <t>SL</t>
   </si>
@@ -403,13 +403,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -726,14 +726,15 @@
     <col min="6" max="6" width="32.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="32.21875" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="30.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="20.77734375" style="7"/>
+    <col min="10" max="10" width="31.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="20.77734375" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="18"/>
+      <c r="B1" s="19"/>
       <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
@@ -879,7 +880,9 @@
       <c r="I3" s="13">
         <v>46272</v>
       </c>
-      <c r="J3" s="13"/>
+      <c r="J3" s="13">
+        <v>46273</v>
+      </c>
       <c r="K3" s="13"/>
       <c r="L3" s="13"/>
       <c r="M3" s="13"/>
@@ -907,7 +910,7 @@
       </c>
       <c r="D4" s="15">
         <f>COUNTIF(E4:X4,"P")/(COUNTIF(E4:X4,"P")+COUNTIF(E4:X4,"A"))</f>
-        <v>0.6</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>45</v>
@@ -924,7 +927,9 @@
       <c r="I4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -953,7 +958,7 @@
       </c>
       <c r="D5" s="15">
         <f t="shared" ref="D5:D41" si="2">COUNTIF(E5:X5,"P")/(COUNTIF(E5:X5,"P")+COUNTIF(E5:X5,"A"))</f>
-        <v>0.6</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>45</v>
@@ -970,7 +975,9 @@
       <c r="I5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -1016,7 +1023,9 @@
       <c r="I6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="1"/>
+      <c r="J6" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -1062,7 +1071,9 @@
       <c r="I7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -1091,7 +1102,7 @@
       </c>
       <c r="D8" s="15">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>45</v>
@@ -1108,7 +1119,9 @@
       <c r="I8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="1"/>
+      <c r="J8" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -1137,7 +1150,7 @@
       </c>
       <c r="D9" s="15">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>45</v>
@@ -1154,7 +1167,9 @@
       <c r="I9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="1"/>
+      <c r="J9" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -1183,7 +1198,7 @@
       </c>
       <c r="D10" s="15">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>45</v>
@@ -1200,7 +1215,9 @@
       <c r="I10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J10" s="1"/>
+      <c r="J10" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1229,7 +1246,7 @@
       </c>
       <c r="D11" s="15">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>45</v>
@@ -1246,7 +1263,9 @@
       <c r="I11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J11" s="1"/>
+      <c r="J11" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -1292,7 +1311,9 @@
       <c r="I12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -1338,7 +1359,9 @@
       <c r="I13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1384,7 +1407,9 @@
       <c r="I14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1430,7 +1455,9 @@
       <c r="I15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="J15" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -1476,7 +1503,9 @@
       <c r="I16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -1522,7 +1551,9 @@
       <c r="I17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J17" s="1"/>
+      <c r="J17" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -1551,7 +1582,7 @@
       </c>
       <c r="D18" s="15">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>45</v>
@@ -1568,7 +1599,9 @@
       <c r="I18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J18" s="1"/>
+      <c r="J18" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -1597,7 +1630,7 @@
       </c>
       <c r="D19" s="15">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>45</v>
@@ -1614,7 +1647,9 @@
       <c r="I19" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J19" s="1"/>
+      <c r="J19" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -1643,7 +1678,7 @@
       </c>
       <c r="D20" s="15">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>45</v>
@@ -1660,7 +1695,9 @@
       <c r="I20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J20" s="1"/>
+      <c r="J20" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1689,7 +1726,7 @@
       </c>
       <c r="D21" s="15">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>43</v>
@@ -1706,7 +1743,9 @@
       <c r="I21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -1752,7 +1791,9 @@
       <c r="I22" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J22" s="1"/>
+      <c r="J22" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -1798,7 +1839,9 @@
       <c r="I23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J23" s="1"/>
+      <c r="J23" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -1827,7 +1870,7 @@
       </c>
       <c r="D24" s="15">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>45</v>
@@ -1844,7 +1887,9 @@
       <c r="I24" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J24" s="1"/>
+      <c r="J24" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -1873,7 +1918,7 @@
       </c>
       <c r="D25" s="15">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>43</v>
@@ -1890,7 +1935,9 @@
       <c r="I25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J25" s="1"/>
+      <c r="J25" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -1936,7 +1983,9 @@
       <c r="I26" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J26" s="1"/>
+      <c r="J26" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -1965,7 +2014,7 @@
       </c>
       <c r="D27" s="15">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>43</v>
@@ -1982,7 +2031,9 @@
       <c r="I27" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J27" s="1"/>
+      <c r="J27" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -2028,7 +2079,9 @@
       <c r="I28" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J28" s="1"/>
+      <c r="J28" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -2074,7 +2127,9 @@
       <c r="I29" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J29" s="1"/>
+      <c r="J29" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -2103,7 +2158,7 @@
       </c>
       <c r="D30" s="15">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>45</v>
@@ -2120,7 +2175,9 @@
       <c r="I30" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -2166,7 +2223,9 @@
       <c r="I31" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J31" s="1"/>
+      <c r="J31" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -2212,7 +2271,9 @@
       <c r="I32" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J32" s="1"/>
+      <c r="J32" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -2258,7 +2319,9 @@
       <c r="I33" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J33" s="1"/>
+      <c r="J33" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -2304,7 +2367,9 @@
       <c r="I34" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="1"/>
+      <c r="J34" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -2350,7 +2415,9 @@
       <c r="I35" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J35" s="1"/>
+      <c r="J35" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2396,7 +2463,9 @@
       <c r="I36" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J36" s="1"/>
+      <c r="J36" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -2442,7 +2511,9 @@
       <c r="I37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J37" s="1"/>
+      <c r="J37" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -2471,7 +2542,7 @@
       </c>
       <c r="D38" s="15">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>43</v>
@@ -2488,7 +2559,9 @@
       <c r="I38" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J38" s="1"/>
+      <c r="J38" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -2534,7 +2607,9 @@
       <c r="I39" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J39" s="1"/>
+      <c r="J39" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2563,7 +2638,7 @@
       </c>
       <c r="D40" s="15">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>45</v>
@@ -2580,7 +2655,9 @@
       <c r="I40" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J40" s="1"/>
+      <c r="J40" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -2609,7 +2686,7 @@
       </c>
       <c r="D41" s="15">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>45</v>
@@ -2626,7 +2703,9 @@
       <c r="I41" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J41" s="1"/>
+      <c r="J41" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -2691,10 +2770,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="18"/>
+      <c r="B1" s="19"/>
       <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
@@ -2710,10 +2789,10 @@
       <c r="G1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="19"/>
+      <c r="I1" s="20"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -2734,8 +2813,8 @@
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -2747,16 +2826,16 @@
       <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="18">
         <v>7.5</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="18">
         <v>7.5</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="18">
         <v>7.5</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="18">
         <v>7.5</v>
       </c>
       <c r="H3" s="16">

--- a/DCE 2-1/Regular Assessment DCE 2-1.xlsx
+++ b/DCE 2-1/Regular Assessment DCE 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\DCE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01103466-D657-41EA-AF83-A39594AC875E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27656CA2-7F18-457B-B8CF-32331EFBF4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Assessment" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!$A$3:$C$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!$A$3:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DCE 2-1 Attendance'!$A$3:$G$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -261,7 +261,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,6 +321,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -350,7 +356,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -412,19 +418,25 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -435,6 +447,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2742,11 +2764,15 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D41">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+      <formula>0.6</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="between">
+      <formula>0.6</formula>
+      <formula>0.89</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2763,9 +2789,10 @@
     <col min="3" max="3" width="43.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="15.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="20" style="7" customWidth="1"/>
+    <col min="8" max="8" width="7.88671875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" style="7" customWidth="1"/>
     <col min="10" max="16384" width="20.77734375" style="7"/>
   </cols>
   <sheetData>
@@ -2839,6 +2866,7 @@
         <v>7.5</v>
       </c>
       <c r="H3" s="16">
+        <f>SUM(D3:G3)</f>
         <v>30</v>
       </c>
       <c r="I3" s="16">
@@ -2855,17 +2883,21 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
+      <c r="D4" s="17">
+        <v>6</v>
+      </c>
+      <c r="E4" s="21">
+        <v>0</v>
+      </c>
       <c r="F4" s="17"/>
       <c r="G4" s="17"/>
       <c r="H4" s="17">
         <f>SUM(D4:G4)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I4" s="17">
-        <f>(H4/20)*7.5</f>
-        <v>0</v>
+        <f>H4/2</f>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -2879,8 +2911,12 @@
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+      <c r="D5" s="21">
+        <v>0</v>
+      </c>
+      <c r="E5" s="21">
+        <v>0</v>
+      </c>
       <c r="F5" s="17"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17">
@@ -2888,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="17">
-        <f t="shared" ref="I5:I41" si="2">(H5/20)*7.5</f>
+        <f t="shared" ref="I5:I41" si="2">H5/2</f>
         <v>0</v>
       </c>
     </row>
@@ -2903,17 +2939,21 @@
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+      <c r="D6" s="17">
+        <v>6</v>
+      </c>
+      <c r="E6" s="17">
+        <v>6</v>
+      </c>
       <c r="F6" s="17"/>
       <c r="G6" s="17"/>
       <c r="H6" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -2927,17 +2967,21 @@
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="D7" s="17">
+        <v>3.75</v>
+      </c>
+      <c r="E7" s="17">
+        <v>6.5</v>
+      </c>
       <c r="F7" s="17"/>
       <c r="G7" s="17"/>
       <c r="H7" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.125</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -2951,8 +2995,12 @@
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+      <c r="D8" s="21">
+        <v>0</v>
+      </c>
+      <c r="E8" s="21">
+        <v>0</v>
+      </c>
       <c r="F8" s="17"/>
       <c r="G8" s="17"/>
       <c r="H8" s="17">
@@ -2975,17 +3023,21 @@
       <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="D9" s="17">
+        <v>7.5</v>
+      </c>
+      <c r="E9" s="17">
+        <v>7</v>
+      </c>
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
       <c r="H9" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -2999,8 +3051,12 @@
       <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
+      <c r="D10" s="21">
+        <v>0</v>
+      </c>
+      <c r="E10" s="21">
+        <v>0</v>
+      </c>
       <c r="F10" s="17"/>
       <c r="G10" s="17"/>
       <c r="H10" s="17">
@@ -3023,17 +3079,21 @@
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="D11" s="17">
+        <v>6.5</v>
+      </c>
+      <c r="E11" s="17">
+        <v>7</v>
+      </c>
       <c r="F11" s="17"/>
       <c r="G11" s="17"/>
       <c r="H11" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="I11" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -3047,17 +3107,21 @@
       <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
+      <c r="D12" s="17">
+        <v>6.5</v>
+      </c>
+      <c r="E12" s="17">
+        <v>7</v>
+      </c>
       <c r="F12" s="17"/>
       <c r="G12" s="17"/>
       <c r="H12" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="I12" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -3071,17 +3135,21 @@
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
+      <c r="D13" s="17">
+        <v>6.5</v>
+      </c>
+      <c r="E13" s="17">
+        <v>6</v>
+      </c>
       <c r="F13" s="17"/>
       <c r="G13" s="17"/>
       <c r="H13" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I13" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -3095,17 +3163,21 @@
       <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
+      <c r="D14" s="17">
+        <v>7</v>
+      </c>
+      <c r="E14" s="17">
+        <v>6</v>
+      </c>
       <c r="F14" s="17"/>
       <c r="G14" s="17"/>
       <c r="H14" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I14" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -3119,17 +3191,21 @@
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
+      <c r="D15" s="17">
+        <v>5</v>
+      </c>
+      <c r="E15" s="17">
+        <v>6</v>
+      </c>
       <c r="F15" s="17"/>
       <c r="G15" s="17"/>
       <c r="H15" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I15" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -3143,17 +3219,21 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
+      <c r="D16" s="17">
+        <v>7.5</v>
+      </c>
+      <c r="E16" s="17">
+        <v>7.5</v>
+      </c>
       <c r="F16" s="17"/>
       <c r="G16" s="17"/>
       <c r="H16" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I16" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -3167,17 +3247,21 @@
       <c r="C17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="D17" s="17">
+        <v>5.5</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3.25</v>
+      </c>
       <c r="F17" s="17"/>
       <c r="G17" s="17"/>
       <c r="H17" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="I17" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.375</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -3191,17 +3275,21 @@
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="D18" s="17">
+        <v>6.5</v>
+      </c>
+      <c r="E18" s="21">
+        <v>0</v>
+      </c>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
       <c r="H18" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -3215,17 +3303,21 @@
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
+      <c r="D19" s="17">
+        <v>6.5</v>
+      </c>
+      <c r="E19" s="21">
+        <v>0</v>
+      </c>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
       <c r="H19" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -3239,17 +3331,21 @@
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="D20" s="17">
+        <v>6</v>
+      </c>
+      <c r="E20" s="21">
+        <v>0</v>
+      </c>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
       <c r="H20" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -3263,17 +3359,21 @@
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="D21" s="17">
+        <v>6</v>
+      </c>
+      <c r="E21" s="17">
+        <v>7</v>
+      </c>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
       <c r="H21" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -3287,17 +3387,21 @@
       <c r="C22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="D22" s="17">
+        <v>6.5</v>
+      </c>
+      <c r="E22" s="21">
+        <v>0</v>
+      </c>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
       <c r="H22" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="I22" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -3311,17 +3415,21 @@
       <c r="C23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="D23" s="17">
+        <v>7</v>
+      </c>
+      <c r="E23" s="17">
+        <v>7</v>
+      </c>
       <c r="F23" s="17"/>
       <c r="G23" s="17"/>
       <c r="H23" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I23" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -3335,17 +3443,21 @@
       <c r="C24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="D24" s="17">
+        <v>6.5</v>
+      </c>
+      <c r="E24" s="17">
+        <v>6.5</v>
+      </c>
       <c r="F24" s="17"/>
       <c r="G24" s="17"/>
       <c r="H24" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I24" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -3359,17 +3471,21 @@
       <c r="C25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="D25" s="17">
+        <v>6</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3.5</v>
+      </c>
       <c r="F25" s="17"/>
       <c r="G25" s="17"/>
       <c r="H25" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="I25" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
@@ -3383,17 +3499,21 @@
       <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
+      <c r="D26" s="17">
+        <v>7.5</v>
+      </c>
+      <c r="E26" s="17">
+        <v>7</v>
+      </c>
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
       <c r="H26" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="I26" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
@@ -3407,8 +3527,12 @@
       <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
+      <c r="D27" s="21">
+        <v>0</v>
+      </c>
+      <c r="E27" s="21">
+        <v>0</v>
+      </c>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
       <c r="H27" s="17">
@@ -3431,17 +3555,21 @@
       <c r="C28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
+      <c r="D28" s="17">
+        <v>7</v>
+      </c>
+      <c r="E28" s="17">
+        <v>7</v>
+      </c>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
       <c r="H28" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I28" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
@@ -3455,17 +3583,21 @@
       <c r="C29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="D29" s="17">
+        <v>7</v>
+      </c>
+      <c r="E29" s="17">
+        <v>7</v>
+      </c>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
       <c r="H29" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
@@ -3479,17 +3611,21 @@
       <c r="C30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
+      <c r="D30" s="17">
+        <v>7</v>
+      </c>
+      <c r="E30" s="17">
+        <v>7</v>
+      </c>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
       <c r="H30" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
@@ -3503,17 +3639,21 @@
       <c r="C31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="D31" s="17">
+        <v>7</v>
+      </c>
+      <c r="E31" s="17">
+        <v>7</v>
+      </c>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
       <c r="H31" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I31" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
@@ -3527,17 +3667,21 @@
       <c r="C32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+      <c r="D32" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="E32" s="1">
+        <v>7</v>
+      </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
@@ -3551,17 +3695,21 @@
       <c r="C33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
+      <c r="D33" s="1">
+        <v>7</v>
+      </c>
+      <c r="E33" s="1">
+        <v>7</v>
+      </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I33" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
@@ -3575,17 +3723,21 @@
       <c r="C34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
+      <c r="D34" s="1">
+        <v>7</v>
+      </c>
+      <c r="E34" s="1">
+        <v>7.5</v>
+      </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="I34" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
@@ -3599,17 +3751,21 @@
       <c r="C35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
+      <c r="D35" s="1">
+        <v>3.75</v>
+      </c>
+      <c r="E35" s="1">
+        <v>6.5</v>
+      </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="I35" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.125</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
@@ -3623,17 +3779,21 @@
       <c r="C36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
+      <c r="D36" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="E36" s="1">
+        <v>7</v>
+      </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="I36" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
@@ -3647,17 +3807,21 @@
       <c r="C37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
+      <c r="D37" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="E37" s="1">
+        <v>6.5</v>
+      </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I37" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -3671,8 +3835,12 @@
       <c r="C38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
+      <c r="D38" s="22">
+        <v>0</v>
+      </c>
+      <c r="E38" s="22">
+        <v>0</v>
+      </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="17">
@@ -3695,8 +3863,12 @@
       <c r="C39" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
+      <c r="D39" s="22">
+        <v>0</v>
+      </c>
+      <c r="E39" s="22">
+        <v>0</v>
+      </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="17">
@@ -3719,8 +3891,12 @@
       <c r="C40" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
+      <c r="D40" s="22">
+        <v>0</v>
+      </c>
+      <c r="E40" s="22">
+        <v>0</v>
+      </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="17">
@@ -3743,21 +3919,25 @@
       <c r="C41" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
+      <c r="D41" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="E41" s="1">
+        <v>3.5</v>
+      </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I41" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:C3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:I3" xr:uid="{2CB2915B-7E74-40B0-9D48-A1940F1D0007}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H1:I2"/>

--- a/DCE 2-1/Regular Assessment DCE 2-1.xlsx
+++ b/DCE 2-1/Regular Assessment DCE 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\DCE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27656CA2-7F18-457B-B8CF-32331EFBF4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94D776B-55FE-46A7-AA45-C611F953E927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!$A$3:$I$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DCE 2-1 Attendance'!$A$3:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DCE 2-1 Attendance'!$A$3:$H$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="56">
   <si>
     <t>SL</t>
   </si>
@@ -204,6 +226,9 @@
   </si>
   <si>
     <t>Knitting Action (Bearded)</t>
+  </si>
+  <si>
+    <t>Marks</t>
   </si>
 </sst>
 </file>
@@ -213,7 +238,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,8 +285,14 @@
       <name val="Gill Sans MT"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Gill Sans MT"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -327,6 +358,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -356,7 +393,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -412,16 +449,34 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -429,7 +484,37 @@
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -457,6 +542,26 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -737,32 +842,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:X44"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.109375" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="32.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="20.77734375" style="7"/>
+    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="32.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="32.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="20.77734375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="23"/>
       <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D1" s="3"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="11"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11"/>
       <c r="I1" s="11"/>
@@ -781,8 +889,9 @@
       <c r="V1" s="11"/>
       <c r="W1" s="11"/>
       <c r="X1" s="11"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y1" s="11"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>40</v>
       </c>
@@ -794,87 +903,88 @@
         <v>41</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="5">
+      <c r="E2" s="3"/>
+      <c r="F2" s="5">
         <v>1</v>
       </c>
-      <c r="F2" s="12">
-        <f>E2+1</f>
+      <c r="G2" s="12">
+        <f>F2+1</f>
         <v>2</v>
       </c>
-      <c r="G2" s="12">
-        <f t="shared" ref="G2:X2" si="0">F2+1</f>
+      <c r="H2" s="12">
+        <f t="shared" ref="H2:Y2" si="0">G2+1</f>
         <v>3</v>
       </c>
-      <c r="H2" s="12">
+      <c r="I2" s="12">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="J2" s="12">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J2" s="12">
+      <c r="K2" s="12">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K2" s="12">
+      <c r="L2" s="12">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="L2" s="12">
+      <c r="M2" s="12">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="M2" s="12">
+      <c r="N2" s="12">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="N2" s="12">
+      <c r="O2" s="12">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O2" s="12">
+      <c r="P2" s="12">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="P2" s="12">
+      <c r="Q2" s="12">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="R2" s="12">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="R2" s="12">
+      <c r="S2" s="12">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="S2" s="12">
+      <c r="T2" s="12">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="T2" s="12">
+      <c r="U2" s="12">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="U2" s="12">
+      <c r="V2" s="12">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="V2" s="12">
+      <c r="W2" s="12">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="W2" s="12">
+      <c r="X2" s="12">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="X2" s="12">
+      <c r="Y2" s="12">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -887,27 +997,33 @@
       <c r="D3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="8">
         <v>46258</v>
       </c>
-      <c r="F3" s="13">
+      <c r="G3" s="13">
         <v>46259</v>
       </c>
-      <c r="G3" s="13">
+      <c r="H3" s="13">
         <v>46265</v>
       </c>
-      <c r="H3" s="13">
+      <c r="I3" s="13">
         <v>46266</v>
       </c>
-      <c r="I3" s="13">
+      <c r="J3" s="13">
         <v>46272</v>
       </c>
-      <c r="J3" s="13">
+      <c r="K3" s="13">
         <v>46273</v>
       </c>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
+      <c r="L3" s="13">
+        <v>46279</v>
+      </c>
+      <c r="M3" s="13">
+        <v>46280</v>
+      </c>
       <c r="N3" s="13"/>
       <c r="O3" s="13"/>
       <c r="P3" s="13"/>
@@ -919,8 +1035,9 @@
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y3" s="13"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -931,30 +1048,37 @@
         <v>3</v>
       </c>
       <c r="D4" s="15">
-        <f>COUNTIF(E4:X4,"P")/(COUNTIF(E4:X4,"P")+COUNTIF(E4:X4,"A"))</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>45</v>
+        <f t="shared" ref="D4:D41" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
+        <v>0.75</v>
+      </c>
+      <c r="E4" s="1" cm="1">
+        <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
@@ -966,10 +1090,11 @@
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y4" s="1"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <f t="shared" ref="A5:A31" si="1">A4+1</f>
+        <f t="shared" ref="A5:A31" si="2">A4+1</f>
         <v>2</v>
       </c>
       <c r="B5" s="1">
@@ -979,30 +1104,37 @@
         <v>4</v>
       </c>
       <c r="D5" s="15">
-        <f t="shared" ref="D5:D41" si="2">COUNTIF(E5:X5,"P")/(COUNTIF(E5:X5,"P")+COUNTIF(E5:X5,"A"))</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="E5" s="1" cm="1">
+        <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,7.5,D5&gt;=80%,6,D5&gt;=70%,4.5,D5&gt;=60%,3,D5&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>43</v>
+      <c r="G5" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>45</v>
+      <c r="I5" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -1014,10 +1146,11 @@
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y5" s="1"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="B6" s="1">
@@ -1027,11 +1160,12 @@
         <v>5</v>
       </c>
       <c r="D6" s="15">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="E6" s="1" cm="1">
+        <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>45</v>
@@ -1048,9 +1182,15 @@
       <c r="J6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -1062,10 +1202,11 @@
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y6" s="1"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="B7" s="1">
@@ -1075,11 +1216,12 @@
         <v>6</v>
       </c>
       <c r="D7" s="15">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="E7" s="1" cm="1">
+        <f t="array" ref="E7">_xlfn.IFS(D7&gt;=90%,7.5,D7&gt;=80%,6,D7&gt;=70%,4.5,D7&gt;=60%,3,D7&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>45</v>
@@ -1096,9 +1238,15 @@
       <c r="J7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -1110,10 +1258,11 @@
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y7" s="1"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="B8" s="1">
@@ -1123,11 +1272,12 @@
         <v>7</v>
       </c>
       <c r="D8" s="15">
-        <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="E8" s="1" cm="1">
+        <f t="array" ref="E8">_xlfn.IFS(D8&gt;=90%,7.5,D8&gt;=80%,6,D8&gt;=70%,4.5,D8&gt;=60%,3,D8&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>45</v>
@@ -1135,18 +1285,24 @@
       <c r="G8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>45</v>
+      <c r="H8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -1158,10 +1314,11 @@
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y8" s="1"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="B9" s="1">
@@ -1171,17 +1328,18 @@
         <v>8</v>
       </c>
       <c r="D9" s="15">
-        <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="E9" s="1" cm="1">
+        <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
+        <v>6</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>45</v>
@@ -1192,9 +1350,15 @@
       <c r="J9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -1206,10 +1370,11 @@
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y9" s="1"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="B10" s="1">
@@ -1219,17 +1384,18 @@
         <v>9</v>
       </c>
       <c r="D10" s="15">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E10" s="1" cm="1">
+        <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
+        <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>43</v>
+      <c r="G10" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>43</v>
@@ -1240,9 +1406,15 @@
       <c r="J10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
+      <c r="K10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -1254,10 +1426,11 @@
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y10" s="1"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="B11" s="1">
@@ -1267,20 +1440,21 @@
         <v>10</v>
       </c>
       <c r="D11" s="15">
-        <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="E11" s="1" cm="1">
+        <f t="array" ref="E11">_xlfn.IFS(D11&gt;=90%,7.5,D11&gt;=80%,6,D11&gt;=70%,4.5,D11&gt;=60%,3,D11&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>45</v>
+      <c r="G11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>45</v>
@@ -1288,9 +1462,15 @@
       <c r="J11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="K11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
@@ -1302,10 +1482,11 @@
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y11" s="1"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="B12" s="1">
@@ -1315,11 +1496,12 @@
         <v>11</v>
       </c>
       <c r="D12" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>45</v>
+      <c r="E12" s="1" cm="1">
+        <f t="array" ref="E12">_xlfn.IFS(D12&gt;=90%,7.5,D12&gt;=80%,6,D12&gt;=70%,4.5,D12&gt;=60%,3,D12&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>45</v>
@@ -1336,9 +1518,15 @@
       <c r="J12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
+      <c r="K12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
@@ -1350,10 +1538,11 @@
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y12" s="1"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="B13" s="1">
@@ -1363,11 +1552,12 @@
         <v>12</v>
       </c>
       <c r="D13" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>45</v>
+      <c r="E13" s="1" cm="1">
+        <f t="array" ref="E13">_xlfn.IFS(D13&gt;=90%,7.5,D13&gt;=80%,6,D13&gt;=70%,4.5,D13&gt;=60%,3,D13&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>45</v>
@@ -1384,9 +1574,15 @@
       <c r="J13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
+      <c r="K13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
@@ -1398,10 +1594,11 @@
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y13" s="1"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="B14" s="1">
@@ -1411,11 +1608,12 @@
         <v>13</v>
       </c>
       <c r="D14" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>45</v>
+      <c r="E14" s="1" cm="1">
+        <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>45</v>
@@ -1432,9 +1630,15 @@
       <c r="J14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
+      <c r="K14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
@@ -1446,10 +1650,11 @@
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y14" s="1"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="B15" s="1">
@@ -1459,11 +1664,12 @@
         <v>14</v>
       </c>
       <c r="D15" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>45</v>
+      <c r="E15" s="1" cm="1">
+        <f t="array" ref="E15">_xlfn.IFS(D15&gt;=90%,7.5,D15&gt;=80%,6,D15&gt;=70%,4.5,D15&gt;=60%,3,D15&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>45</v>
@@ -1480,9 +1686,15 @@
       <c r="J15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
@@ -1494,10 +1706,11 @@
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y15" s="1"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="B16" s="1">
@@ -1507,11 +1720,12 @@
         <v>15</v>
       </c>
       <c r="D16" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>45</v>
+      <c r="E16" s="1" cm="1">
+        <f t="array" ref="E16">_xlfn.IFS(D16&gt;=90%,7.5,D16&gt;=80%,6,D16&gt;=70%,4.5,D16&gt;=60%,3,D16&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>45</v>
@@ -1528,9 +1742,15 @@
       <c r="J16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
+      <c r="K16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
@@ -1542,10 +1762,11 @@
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y16" s="1"/>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="B17" s="1">
@@ -1555,11 +1776,12 @@
         <v>16</v>
       </c>
       <c r="D17" s="15">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="E17" s="1" cm="1">
+        <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>45</v>
@@ -1576,9 +1798,15 @@
       <c r="J17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
@@ -1590,10 +1818,11 @@
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y17" s="1"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="B18" s="1">
@@ -1603,11 +1832,12 @@
         <v>17</v>
       </c>
       <c r="D18" s="15">
-        <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="E18" s="1" cm="1">
+        <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,7.5,D18&gt;=80%,6,D18&gt;=70%,4.5,D18&gt;=60%,3,D18&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>45</v>
@@ -1618,15 +1848,21 @@
       <c r="H18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
+      <c r="I18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
@@ -1638,10 +1874,11 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y18" s="1"/>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="B19" s="1">
@@ -1651,11 +1888,12 @@
         <v>18</v>
       </c>
       <c r="D19" s="15">
-        <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="E19" s="1" cm="1">
+        <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>45</v>
@@ -1666,15 +1904,21 @@
       <c r="H19" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
+      <c r="I19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
@@ -1686,10 +1930,11 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y19" s="1"/>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="B20" s="1">
@@ -1699,11 +1944,12 @@
         <v>19</v>
       </c>
       <c r="D20" s="15">
-        <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="E20" s="1" cm="1">
+        <f t="array" ref="E20">_xlfn.IFS(D20&gt;=90%,7.5,D20&gt;=80%,6,D20&gt;=70%,4.5,D20&gt;=60%,3,D20&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>45</v>
@@ -1714,15 +1960,21 @@
       <c r="H20" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I20" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
+      <c r="I20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
@@ -1734,10 +1986,11 @@
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y20" s="1"/>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="B21" s="1">
@@ -1747,14 +2000,15 @@
         <v>20</v>
       </c>
       <c r="D21" s="15">
-        <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="E21" s="1" cm="1">
+        <f t="array" ref="E21">_xlfn.IFS(D21&gt;=90%,7.5,D21&gt;=80%,6,D21&gt;=70%,4.5,D21&gt;=60%,3,D21&lt;60%,0)</f>
+        <v>6</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>45</v>
@@ -1768,9 +2022,15 @@
       <c r="J21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
+      <c r="K21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
@@ -1782,10 +2042,11 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y21" s="1"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="B22" s="1">
@@ -1795,11 +2056,12 @@
         <v>21</v>
       </c>
       <c r="D22" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>45</v>
+      <c r="E22" s="1" cm="1">
+        <f t="array" ref="E22">_xlfn.IFS(D22&gt;=90%,7.5,D22&gt;=80%,6,D22&gt;=70%,4.5,D22&gt;=60%,3,D22&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>45</v>
@@ -1816,9 +2078,15 @@
       <c r="J22" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
+      <c r="K22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
@@ -1830,10 +2098,11 @@
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y22" s="1"/>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="B23" s="1">
@@ -1843,11 +2112,12 @@
         <v>22</v>
       </c>
       <c r="D23" s="15">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="E23" s="1" cm="1">
+        <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>45</v>
@@ -1864,9 +2134,15 @@
       <c r="J23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
+      <c r="K23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -1878,10 +2154,11 @@
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y23" s="1"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="B24" s="1">
@@ -1891,30 +2168,37 @@
         <v>23</v>
       </c>
       <c r="D24" s="15">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="E24" s="1" cm="1">
+        <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G24" s="6" t="s">
-        <v>43</v>
+      <c r="G24" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>45</v>
+      <c r="I24" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
+      <c r="K24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -1926,10 +2210,11 @@
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y24" s="1"/>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="B25" s="1">
@@ -1939,14 +2224,15 @@
         <v>24</v>
       </c>
       <c r="D25" s="15">
-        <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="E25" s="1" cm="1">
+        <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>45</v>
@@ -1960,9 +2246,15 @@
       <c r="J25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
+      <c r="K25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
@@ -1974,10 +2266,11 @@
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y25" s="1"/>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="B26" s="1">
@@ -1987,11 +2280,12 @@
         <v>25</v>
       </c>
       <c r="D26" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>45</v>
+      <c r="E26" s="1" cm="1">
+        <f t="array" ref="E26">_xlfn.IFS(D26&gt;=90%,7.5,D26&gt;=80%,6,D26&gt;=70%,4.5,D26&gt;=60%,3,D26&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>45</v>
@@ -2008,9 +2302,15 @@
       <c r="J26" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
+      <c r="K26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -2022,10 +2322,11 @@
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y26" s="1"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="B27" s="1">
@@ -2035,14 +2336,15 @@
         <v>26</v>
       </c>
       <c r="D27" s="15">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="E27" s="1" cm="1">
+        <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,7.5,D27&gt;=80%,6,D27&gt;=70%,4.5,D27&gt;=60%,3,D27&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>45</v>
@@ -2050,15 +2352,21 @@
       <c r="H27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I27" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
+      <c r="I27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
@@ -2070,10 +2378,11 @@
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y27" s="1"/>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="B28" s="1">
@@ -2083,11 +2392,12 @@
         <v>27</v>
       </c>
       <c r="D28" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>45</v>
+      <c r="E28" s="1" cm="1">
+        <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>45</v>
@@ -2104,9 +2414,15 @@
       <c r="J28" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
+      <c r="K28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
@@ -2118,10 +2434,11 @@
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y28" s="1"/>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="B29" s="1">
@@ -2131,11 +2448,12 @@
         <v>28</v>
       </c>
       <c r="D29" s="15">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="E29" s="1" cm="1">
+        <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>45</v>
@@ -2152,9 +2470,15 @@
       <c r="J29" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
+      <c r="K29" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
@@ -2166,10 +2490,11 @@
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y29" s="1"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="B30" s="1">
@@ -2179,30 +2504,37 @@
         <v>29</v>
       </c>
       <c r="D30" s="15">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.625</v>
+      </c>
+      <c r="E30" s="1" cm="1">
+        <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
+        <v>3</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>43</v>
+      <c r="G30" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I30" s="1" t="s">
-        <v>45</v>
+      <c r="I30" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
+      <c r="K30" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
@@ -2214,10 +2546,11 @@
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y30" s="1"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="B31" s="1">
@@ -2227,11 +2560,12 @@
         <v>30</v>
       </c>
       <c r="D31" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>45</v>
+      <c r="E31" s="1" cm="1">
+        <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>45</v>
@@ -2248,9 +2582,15 @@
       <c r="J31" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
+      <c r="K31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
@@ -2262,8 +2602,9 @@
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y31" s="1"/>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f t="shared" ref="A32:A41" si="3">A31+1</f>
         <v>29</v>
@@ -2275,11 +2616,12 @@
         <v>31</v>
       </c>
       <c r="D32" s="15">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="E32" s="1" cm="1">
+        <f t="array" ref="E32">_xlfn.IFS(D32&gt;=90%,7.5,D32&gt;=80%,6,D32&gt;=70%,4.5,D32&gt;=60%,3,D32&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>45</v>
@@ -2296,9 +2638,15 @@
       <c r="J32" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
+      <c r="K32" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
@@ -2310,8 +2658,9 @@
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y32" s="1"/>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -2323,11 +2672,12 @@
         <v>32</v>
       </c>
       <c r="D33" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>45</v>
+      <c r="E33" s="1" cm="1">
+        <f t="array" ref="E33">_xlfn.IFS(D33&gt;=90%,7.5,D33&gt;=80%,6,D33&gt;=70%,4.5,D33&gt;=60%,3,D33&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>45</v>
@@ -2344,9 +2694,15 @@
       <c r="J33" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
+      <c r="K33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
@@ -2358,8 +2714,9 @@
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y33" s="1"/>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f t="shared" si="3"/>
         <v>31</v>
@@ -2371,11 +2728,12 @@
         <v>33</v>
       </c>
       <c r="D34" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>45</v>
+      <c r="E34" s="1" cm="1">
+        <f t="array" ref="E34">_xlfn.IFS(D34&gt;=90%,7.5,D34&gt;=80%,6,D34&gt;=70%,4.5,D34&gt;=60%,3,D34&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>45</v>
@@ -2392,9 +2750,15 @@
       <c r="J34" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
+      <c r="K34" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
@@ -2406,8 +2770,9 @@
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y34" s="1"/>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f t="shared" si="3"/>
         <v>32</v>
@@ -2419,11 +2784,12 @@
         <v>34</v>
       </c>
       <c r="D35" s="15">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="E35" s="1" cm="1">
+        <f t="array" ref="E35">_xlfn.IFS(D35&gt;=90%,7.5,D35&gt;=80%,6,D35&gt;=70%,4.5,D35&gt;=60%,3,D35&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>45</v>
@@ -2440,9 +2806,15 @@
       <c r="J35" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
+      <c r="K35" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
@@ -2454,8 +2826,9 @@
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y35" s="1"/>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f t="shared" si="3"/>
         <v>33</v>
@@ -2467,11 +2840,12 @@
         <v>35</v>
       </c>
       <c r="D36" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>45</v>
+      <c r="E36" s="1" cm="1">
+        <f t="array" ref="E36">_xlfn.IFS(D36&gt;=90%,7.5,D36&gt;=80%,6,D36&gt;=70%,4.5,D36&gt;=60%,3,D36&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>45</v>
@@ -2488,9 +2862,15 @@
       <c r="J36" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
+      <c r="K36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
@@ -2502,8 +2882,9 @@
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y36" s="1"/>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f t="shared" si="3"/>
         <v>34</v>
@@ -2515,11 +2896,12 @@
         <v>36</v>
       </c>
       <c r="D37" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>45</v>
+      <c r="E37" s="1" cm="1">
+        <f t="array" ref="E37">_xlfn.IFS(D37&gt;=90%,7.5,D37&gt;=80%,6,D37&gt;=70%,4.5,D37&gt;=60%,3,D37&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>45</v>
@@ -2536,9 +2918,15 @@
       <c r="J37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
+      <c r="K37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
@@ -2550,8 +2938,9 @@
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y37" s="1"/>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <f t="shared" si="3"/>
         <v>35</v>
@@ -2563,20 +2952,21 @@
         <v>37</v>
       </c>
       <c r="D38" s="15">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.375</v>
+      </c>
+      <c r="E38" s="1" cm="1">
+        <f t="array" ref="E38">_xlfn.IFS(D38&gt;=90%,7.5,D38&gt;=80%,6,D38&gt;=70%,4.5,D38&gt;=60%,3,D38&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H38" s="6" t="s">
-        <v>43</v>
+      <c r="H38" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="I38" s="6" t="s">
         <v>43</v>
@@ -2584,9 +2974,15 @@
       <c r="J38" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
+      <c r="K38" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
@@ -2598,56 +2994,65 @@
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
+      <c r="Y38" s="1"/>
+    </row>
+    <row r="39" spans="1:25" s="28" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="25">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="25">
         <v>25010901040</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D39" s="15">
-        <f t="shared" si="2"/>
+      <c r="D39" s="26">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J39" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="E39" s="25" cm="1">
+        <f t="array" ref="E39">_xlfn.IFS(D39&gt;=90%,7.5,D39&gt;=80%,6,D39&gt;=70%,4.5,D39&gt;=60%,3,D39&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="G39" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="H39" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="I39" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="J39" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="K39" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="L39" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="M39" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="N39" s="25"/>
+      <c r="O39" s="25"/>
+      <c r="P39" s="25"/>
+      <c r="Q39" s="25"/>
+      <c r="R39" s="25"/>
+      <c r="S39" s="25"/>
+      <c r="T39" s="25"/>
+      <c r="U39" s="25"/>
+      <c r="V39" s="25"/>
+      <c r="W39" s="25"/>
+      <c r="X39" s="25"/>
+      <c r="Y39" s="25"/>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <f t="shared" si="3"/>
         <v>37</v>
@@ -2659,30 +3064,37 @@
         <v>44</v>
       </c>
       <c r="D40" s="15">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.625</v>
+      </c>
+      <c r="E40" s="1" cm="1">
+        <f t="array" ref="E40">_xlfn.IFS(D40&gt;=90%,7.5,D40&gt;=80%,6,D40&gt;=70%,4.5,D40&gt;=60%,3,D40&lt;60%,0)</f>
+        <v>3</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G40" s="6" t="s">
-        <v>43</v>
+      <c r="G40" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>45</v>
+      <c r="I40" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
+      <c r="K40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
@@ -2694,8 +3106,9 @@
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
       <c r="X40" s="1"/>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y40" s="1"/>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <f t="shared" si="3"/>
         <v>38</v>
@@ -2707,30 +3120,37 @@
         <v>38</v>
       </c>
       <c r="D41" s="15">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="E41" s="1" cm="1">
+        <f t="array" ref="E41">_xlfn.IFS(D41&gt;=90%,7.5,D41&gt;=80%,6,D41&gt;=70%,4.5,D41&gt;=60%,3,D41&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>45</v>
+      <c r="G41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
+      <c r="J41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
@@ -2742,37 +3162,57 @@
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="F42" s="14"/>
+      <c r="Y41" s="1"/>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="E42" s="7"/>
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="F43" s="14"/>
+      <c r="I42" s="14"/>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="F44" s="14"/>
+      <c r="I43" s="14"/>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:H3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D41">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
+      <formula>0.79</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+      <formula>0.89</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="lessThan">
       <formula>0.6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="between">
       <formula>0.6</formula>
       <formula>0.89</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:E41">
+    <cfRule type="cellIs" dxfId="2" priority="12" operator="lessThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="13" operator="between">
+      <formula>2</formula>
+      <formula>5.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="14" operator="greaterThan">
+      <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2797,10 +3237,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="23"/>
       <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
@@ -2816,10 +3256,10 @@
       <c r="G1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="20"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -2840,8 +3280,8 @@
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
     </row>
     <row r="3" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -2887,17 +3327,17 @@
         <v>6</v>
       </c>
       <c r="E4" s="21">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="F4" s="17"/>
       <c r="G4" s="17"/>
       <c r="H4" s="17">
         <f>SUM(D4:G4)</f>
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="I4" s="17">
         <f>H4/2</f>
-        <v>3</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -2912,20 +3352,20 @@
         <v>4</v>
       </c>
       <c r="D5" s="21">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="E5" s="21">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17">
         <f t="shared" ref="H5:H41" si="1">SUM(D5:G5)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" ref="I5:I41" si="2">H5/2</f>
-        <v>0</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -2995,10 +3435,10 @@
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="19">
         <v>0</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="19">
         <v>0</v>
       </c>
       <c r="F8" s="17"/>
@@ -3051,10 +3491,10 @@
       <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="19">
         <v>0</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="19">
         <v>0</v>
       </c>
       <c r="F10" s="17"/>
@@ -3279,17 +3719,17 @@
         <v>6.5</v>
       </c>
       <c r="E18" s="21">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
       <c r="H18" s="17">
         <f t="shared" si="1"/>
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="I18" s="17">
         <f t="shared" si="2"/>
-        <v>3.25</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -3307,17 +3747,17 @@
         <v>6.5</v>
       </c>
       <c r="E19" s="21">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
       <c r="H19" s="17">
         <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="I19" s="17">
+        <f t="shared" si="2"/>
         <v>6.5</v>
-      </c>
-      <c r="I19" s="17">
-        <f t="shared" si="2"/>
-        <v>3.25</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -3335,17 +3775,17 @@
         <v>6</v>
       </c>
       <c r="E20" s="21">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
       <c r="H20" s="17">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="I20" s="17">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -3390,7 +3830,7 @@
       <c r="D22" s="17">
         <v>6.5</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="19">
         <v>0</v>
       </c>
       <c r="F22" s="17"/>
@@ -3528,20 +3968,20 @@
         <v>26</v>
       </c>
       <c r="D27" s="21">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E27" s="21">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
       <c r="H27" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
@@ -3835,10 +4275,10 @@
       <c r="C38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="20">
         <v>0</v>
       </c>
-      <c r="E38" s="22">
+      <c r="E38" s="20">
         <v>0</v>
       </c>
       <c r="F38" s="1"/>
@@ -3863,10 +4303,10 @@
       <c r="C39" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="20">
         <v>0</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="20">
         <v>0</v>
       </c>
       <c r="F39" s="1"/>
@@ -3892,20 +4332,20 @@
         <v>44</v>
       </c>
       <c r="D40" s="22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E40" s="22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="I40" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">

--- a/DCE 2-1/Regular Assessment DCE 2-1.xlsx
+++ b/DCE 2-1/Regular Assessment DCE 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\DCE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94D776B-55FE-46A7-AA45-C611F953E927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0B0A50-226F-4189-961A-7D5892AB17B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Assessment" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!$A$3:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!$A$3:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DCE 2-1 Attendance'!$A$3:$H$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="55">
   <si>
     <t>SL</t>
   </si>
@@ -204,21 +204,12 @@
     <t>Attendance%</t>
   </si>
   <si>
-    <t>K. M. AMINUL ISLAM SIAM</t>
-  </si>
-  <si>
     <t>Assignment 1</t>
   </si>
   <si>
-    <t>Assignmnet 2</t>
-  </si>
-  <si>
     <t>Assignment 3</t>
   </si>
   <si>
-    <t>Assignmnet 4</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -229,6 +220,12 @@
   </si>
   <si>
     <t>Marks</t>
+  </si>
+  <si>
+    <t>Knitting Action (Tuck, Miss)</t>
+  </si>
+  <si>
+    <t>Assignment 2</t>
   </si>
 </sst>
 </file>
@@ -238,7 +235,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,12 +279,6 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Gill Sans MT"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Gill Sans MT"/>
       <family val="2"/>
     </font>
@@ -393,7 +384,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -467,16 +458,13 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -842,7 +830,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" style="7" bestFit="1" customWidth="1"/>
@@ -857,7 +845,8 @@
     <col min="11" max="11" width="31.21875" style="7" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="32.33203125" style="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="32.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="20.77734375" style="7"/>
+    <col min="14" max="14" width="32.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="20.77734375" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -896,8 +885,8 @@
         <v>40</v>
       </c>
       <c r="B2" s="3">
-        <f>COUNT(A4:A41)</f>
-        <v>38</v>
+        <f>COUNT(A4:A40)</f>
+        <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>41</v>
@@ -998,7 +987,7 @@
         <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F3" s="8">
         <v>46258</v>
@@ -1024,7 +1013,9 @@
       <c r="M3" s="13">
         <v>46280</v>
       </c>
-      <c r="N3" s="13"/>
+      <c r="N3" s="13">
+        <v>46286</v>
+      </c>
       <c r="O3" s="13"/>
       <c r="P3" s="13"/>
       <c r="Q3" s="13"/>
@@ -1048,8 +1039,8 @@
         <v>3</v>
       </c>
       <c r="D4" s="15">
-        <f t="shared" ref="D4:D41" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
-        <v>0.75</v>
+        <f t="shared" ref="D4:D40" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E4" s="1" cm="1">
         <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
@@ -1079,7 +1070,9 @@
       <c r="M4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="1"/>
+      <c r="N4" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -1105,7 +1098,7 @@
       </c>
       <c r="D5" s="15">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E5" s="1" cm="1">
         <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,7.5,D5&gt;=80%,6,D5&gt;=70%,4.5,D5&gt;=60%,3,D5&lt;60%,0)</f>
@@ -1135,7 +1128,9 @@
       <c r="M5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N5" s="1"/>
+      <c r="N5" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
@@ -1161,7 +1156,7 @@
       </c>
       <c r="D6" s="15">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E6" s="1" cm="1">
         <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
@@ -1191,7 +1186,9 @@
       <c r="M6" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="N6" s="1"/>
+      <c r="N6" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -1217,7 +1214,7 @@
       </c>
       <c r="D7" s="15">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E7" s="1" cm="1">
         <f t="array" ref="E7">_xlfn.IFS(D7&gt;=90%,7.5,D7&gt;=80%,6,D7&gt;=70%,4.5,D7&gt;=60%,3,D7&lt;60%,0)</f>
@@ -1247,7 +1244,9 @@
       <c r="M7" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="1"/>
+      <c r="N7" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
@@ -1273,7 +1272,7 @@
       </c>
       <c r="D8" s="15">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E8" s="1" cm="1">
         <f t="array" ref="E8">_xlfn.IFS(D8&gt;=90%,7.5,D8&gt;=80%,6,D8&gt;=70%,4.5,D8&gt;=60%,3,D8&lt;60%,0)</f>
@@ -1303,7 +1302,9 @@
       <c r="M8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N8" s="1"/>
+      <c r="N8" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -1329,11 +1330,11 @@
       </c>
       <c r="D9" s="15">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E9" s="1" cm="1">
         <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>45</v>
@@ -1359,7 +1360,9 @@
       <c r="M9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N9" s="1"/>
+      <c r="N9" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -1385,7 +1388,7 @@
       </c>
       <c r="D10" s="15">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
@@ -1415,7 +1418,9 @@
       <c r="M10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="N10" s="1"/>
+      <c r="N10" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -1441,7 +1446,7 @@
       </c>
       <c r="D11" s="15">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E11" s="1" cm="1">
         <f t="array" ref="E11">_xlfn.IFS(D11&gt;=90%,7.5,D11&gt;=80%,6,D11&gt;=70%,4.5,D11&gt;=60%,3,D11&lt;60%,0)</f>
@@ -1471,7 +1476,9 @@
       <c r="M11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="N11" s="1"/>
+      <c r="N11" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -1527,7 +1534,9 @@
       <c r="M12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N12" s="1"/>
+      <c r="N12" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
@@ -1583,7 +1592,9 @@
       <c r="M13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N13" s="1"/>
+      <c r="N13" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
@@ -1609,11 +1620,11 @@
       </c>
       <c r="D14" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E14" s="1" cm="1">
         <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>45</v>
@@ -1639,7 +1650,9 @@
       <c r="M14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N14" s="1"/>
+      <c r="N14" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -1695,7 +1708,9 @@
       <c r="M15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
@@ -1751,7 +1766,9 @@
       <c r="M16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N16" s="1"/>
+      <c r="N16" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
@@ -1777,7 +1794,7 @@
       </c>
       <c r="D17" s="15">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E17" s="1" cm="1">
         <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
@@ -1807,7 +1824,9 @@
       <c r="M17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="N17" s="1"/>
+      <c r="N17" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
@@ -1833,7 +1852,7 @@
       </c>
       <c r="D18" s="15">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E18" s="1" cm="1">
         <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,7.5,D18&gt;=80%,6,D18&gt;=70%,4.5,D18&gt;=60%,3,D18&lt;60%,0)</f>
@@ -1863,7 +1882,9 @@
       <c r="M18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N18" s="1"/>
+      <c r="N18" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
@@ -1889,7 +1910,7 @@
       </c>
       <c r="D19" s="15">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E19" s="1" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
@@ -1919,7 +1940,9 @@
       <c r="M19" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N19" s="1"/>
+      <c r="N19" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
@@ -1945,7 +1968,7 @@
       </c>
       <c r="D20" s="15">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E20" s="1" cm="1">
         <f t="array" ref="E20">_xlfn.IFS(D20&gt;=90%,7.5,D20&gt;=80%,6,D20&gt;=70%,4.5,D20&gt;=60%,3,D20&lt;60%,0)</f>
@@ -1975,7 +1998,9 @@
       <c r="M20" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N20" s="1"/>
+      <c r="N20" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
@@ -2001,11 +2026,11 @@
       </c>
       <c r="D21" s="15">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E21" s="1" cm="1">
         <f t="array" ref="E21">_xlfn.IFS(D21&gt;=90%,7.5,D21&gt;=80%,6,D21&gt;=70%,4.5,D21&gt;=60%,3,D21&lt;60%,0)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>43</v>
@@ -2031,7 +2056,9 @@
       <c r="M21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N21" s="1"/>
+      <c r="N21" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
@@ -2087,7 +2114,9 @@
       <c r="M22" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N22" s="1"/>
+      <c r="N22" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
@@ -2113,7 +2142,7 @@
       </c>
       <c r="D23" s="15">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E23" s="1" cm="1">
         <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
@@ -2143,7 +2172,9 @@
       <c r="M23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="N23" s="1"/>
+      <c r="N23" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -2169,7 +2200,7 @@
       </c>
       <c r="D24" s="15">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E24" s="1" cm="1">
         <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
@@ -2199,7 +2230,9 @@
       <c r="M24" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N24" s="1"/>
+      <c r="N24" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -2225,7 +2258,7 @@
       </c>
       <c r="D25" s="15">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E25" s="1" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
@@ -2255,7 +2288,9 @@
       <c r="M25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N25" s="1"/>
+      <c r="N25" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -2311,7 +2346,9 @@
       <c r="M26" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N26" s="1"/>
+      <c r="N26" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
@@ -2337,7 +2374,7 @@
       </c>
       <c r="D27" s="15">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E27" s="1" cm="1">
         <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,7.5,D27&gt;=80%,6,D27&gt;=70%,4.5,D27&gt;=60%,3,D27&lt;60%,0)</f>
@@ -2367,7 +2404,9 @@
       <c r="M27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N27" s="1"/>
+      <c r="N27" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -2423,7 +2462,9 @@
       <c r="M28" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N28" s="1"/>
+      <c r="N28" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
@@ -2449,7 +2490,7 @@
       </c>
       <c r="D29" s="15">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E29" s="1" cm="1">
         <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
@@ -2479,7 +2520,9 @@
       <c r="M29" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N29" s="1"/>
+      <c r="N29" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
@@ -2505,7 +2548,7 @@
       </c>
       <c r="D30" s="15">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E30" s="1" cm="1">
         <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
@@ -2535,7 +2578,9 @@
       <c r="M30" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N30" s="1"/>
+      <c r="N30" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
@@ -2591,7 +2636,9 @@
       <c r="M31" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N31" s="1"/>
+      <c r="N31" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
@@ -2606,7 +2653,7 @@
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <f t="shared" ref="A32:A41" si="3">A31+1</f>
+        <f t="shared" ref="A32:A40" si="3">A31+1</f>
         <v>29</v>
       </c>
       <c r="B32" s="1">
@@ -2617,7 +2664,7 @@
       </c>
       <c r="D32" s="15">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E32" s="1" cm="1">
         <f t="array" ref="E32">_xlfn.IFS(D32&gt;=90%,7.5,D32&gt;=80%,6,D32&gt;=70%,4.5,D32&gt;=60%,3,D32&lt;60%,0)</f>
@@ -2647,7 +2694,9 @@
       <c r="M32" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N32" s="1"/>
+      <c r="N32" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
@@ -2703,7 +2752,9 @@
       <c r="M33" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N33" s="1"/>
+      <c r="N33" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
@@ -2759,7 +2810,9 @@
       <c r="M34" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N34" s="1"/>
+      <c r="N34" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
@@ -2785,7 +2838,7 @@
       </c>
       <c r="D35" s="15">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E35" s="1" cm="1">
         <f t="array" ref="E35">_xlfn.IFS(D35&gt;=90%,7.5,D35&gt;=80%,6,D35&gt;=70%,4.5,D35&gt;=60%,3,D35&lt;60%,0)</f>
@@ -2815,7 +2868,9 @@
       <c r="M35" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="N35" s="1"/>
+      <c r="N35" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
@@ -2841,11 +2896,11 @@
       </c>
       <c r="D36" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E36" s="1" cm="1">
         <f t="array" ref="E36">_xlfn.IFS(D36&gt;=90%,7.5,D36&gt;=80%,6,D36&gt;=70%,4.5,D36&gt;=60%,3,D36&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>45</v>
@@ -2871,7 +2926,9 @@
       <c r="M36" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N36" s="1"/>
+      <c r="N36" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
@@ -2927,7 +2984,9 @@
       <c r="M37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N37" s="1"/>
+      <c r="N37" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
@@ -2953,7 +3012,7 @@
       </c>
       <c r="D38" s="15">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="E38" s="1" cm="1">
         <f t="array" ref="E38">_xlfn.IFS(D38&gt;=90%,7.5,D38&gt;=80%,6,D38&gt;=70%,4.5,D38&gt;=60%,3,D38&lt;60%,0)</f>
@@ -2983,7 +3042,9 @@
       <c r="M38" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N38" s="1"/>
+      <c r="N38" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
@@ -2996,61 +3057,63 @@
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
     </row>
-    <row r="39" spans="1:25" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="B39" s="25">
-        <v>25010901040</v>
-      </c>
-      <c r="C39" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="D39" s="26">
+      <c r="B39" s="1">
+        <v>24010901023</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E39" s="25" cm="1">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="E39" s="1" cm="1">
         <f t="array" ref="E39">_xlfn.IFS(D39&gt;=90%,7.5,D39&gt;=80%,6,D39&gt;=70%,4.5,D39&gt;=60%,3,D39&lt;60%,0)</f>
         <v>0</v>
       </c>
-      <c r="F39" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="G39" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="H39" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="I39" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="J39" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="K39" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="L39" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="M39" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="N39" s="25"/>
-      <c r="O39" s="25"/>
-      <c r="P39" s="25"/>
-      <c r="Q39" s="25"/>
-      <c r="R39" s="25"/>
-      <c r="S39" s="25"/>
-      <c r="T39" s="25"/>
-      <c r="U39" s="25"/>
-      <c r="V39" s="25"/>
-      <c r="W39" s="25"/>
-      <c r="X39" s="25"/>
-      <c r="Y39" s="25"/>
+      <c r="F39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
@@ -3058,14 +3121,14 @@
         <v>37</v>
       </c>
       <c r="B40" s="1">
-        <v>24010901023</v>
+        <v>24010901033</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D40" s="15">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E40" s="1" cm="1">
         <f t="array" ref="E40">_xlfn.IFS(D40&gt;=90%,7.5,D40&gt;=80%,6,D40&gt;=70%,4.5,D40&gt;=60%,3,D40&lt;60%,0)</f>
@@ -3080,22 +3143,24 @@
       <c r="H40" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I40" s="6" t="s">
-        <v>43</v>
+      <c r="I40" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>45</v>
+      <c r="K40" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="M40" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="N40" s="1"/>
+      <c r="M40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
@@ -3109,63 +3174,12 @@
       <c r="Y40" s="1"/>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
-        <f t="shared" si="3"/>
-        <v>38</v>
-      </c>
-      <c r="B41" s="1">
-        <v>24010901033</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" s="15">
-        <f t="shared" si="1"/>
-        <v>0.75</v>
-      </c>
-      <c r="E41" s="1" cm="1">
-        <f t="array" ref="E41">_xlfn.IFS(D41&gt;=90%,7.5,D41&gt;=80%,6,D41&gt;=70%,4.5,D41&gt;=60%,3,D41&lt;60%,0)</f>
-        <v>4.5</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
-      <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1"/>
-      <c r="W41" s="1"/>
-      <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
+      <c r="E41" s="7"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="E42" s="7"/>
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
       <c r="I42" s="14"/>
@@ -3174,18 +3188,13 @@
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
       <c r="I43" s="14"/>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D41">
+  <conditionalFormatting sqref="D4:D40">
     <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
       <formula>0.79</formula>
     </cfRule>
@@ -3203,7 +3212,7 @@
       <formula>0.89</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E41">
+  <conditionalFormatting sqref="E4:E40">
     <cfRule type="cellIs" dxfId="2" priority="12" operator="lessThan">
       <formula>3</formula>
     </cfRule>
@@ -3221,7 +3230,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CB2915B-7E74-40B0-9D48-A1940F1D0007}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" style="7" bestFit="1" customWidth="1"/>
@@ -3229,14 +3238,13 @@
     <col min="3" max="3" width="43.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" style="7" customWidth="1"/>
-    <col min="7" max="7" width="20" style="7" customWidth="1"/>
-    <col min="8" max="8" width="7.88671875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="20.77734375" style="7"/>
+    <col min="6" max="6" width="31" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="20.77734375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>42</v>
       </c>
@@ -3245,45 +3253,43 @@
         <v>39</v>
       </c>
       <c r="D1" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="G1" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="I1" s="24"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H1" s="24"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B2" s="3">
-        <f>COUNT(A4:A41)</f>
-        <v>38</v>
+        <f>COUNT(A4:A40)</f>
+        <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
+      <c r="G2" s="24"/>
       <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-    </row>
-    <row r="3" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -3302,18 +3308,15 @@
       <c r="F3" s="18">
         <v>7.5</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="16">
+        <f>SUM(D3:F3)</f>
+        <v>22.5</v>
+      </c>
+      <c r="H3" s="25">
         <v>7.5</v>
       </c>
-      <c r="H3" s="16">
-        <f>SUM(D3:G3)</f>
-        <v>30</v>
-      </c>
-      <c r="I3" s="16">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3330,19 +3333,18 @@
         <v>6.5</v>
       </c>
       <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17">
-        <f>SUM(D4:G4)</f>
+      <c r="G4" s="17">
+        <f>SUM(D4:F4)</f>
         <v>12.5</v>
       </c>
-      <c r="I4" s="17">
-        <f>H4/2</f>
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H4" s="26">
+        <f>G4/3</f>
+        <v>4.166666666666667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <f t="shared" ref="A5:A41" si="0">A4+1</f>
+        <f t="shared" ref="A5:A40" si="0">A4+1</f>
         <v>2</v>
       </c>
       <c r="B5" s="1">
@@ -3358,17 +3360,16 @@
         <v>3.25</v>
       </c>
       <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17">
-        <f t="shared" ref="H5:H41" si="1">SUM(D5:G5)</f>
+      <c r="G5" s="17">
+        <f>SUM(D5:F5)</f>
         <v>7</v>
       </c>
-      <c r="I5" s="17">
-        <f t="shared" ref="I5:I41" si="2">H5/2</f>
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H5" s="26">
+        <f t="shared" ref="H5:H8" si="1">G5/3</f>
+        <v>2.3333333333333335</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -3386,17 +3387,16 @@
         <v>6</v>
       </c>
       <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17">
+      <c r="G6" s="17">
+        <f>SUM(D6:F6)</f>
+        <v>12</v>
+      </c>
+      <c r="H6" s="26">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="I6" s="17">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3414,17 +3414,16 @@
         <v>6.5</v>
       </c>
       <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17">
+      <c r="G7" s="17">
+        <f>SUM(D7:F7)</f>
+        <v>10.25</v>
+      </c>
+      <c r="H7" s="26">
         <f t="shared" si="1"/>
-        <v>10.25</v>
-      </c>
-      <c r="I7" s="17">
-        <f t="shared" si="2"/>
-        <v>5.125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>3.4166666666666665</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3442,17 +3441,16 @@
         <v>0</v>
       </c>
       <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17">
+      <c r="G8" s="17">
+        <f>SUM(D8:F8)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="26">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I8" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3470,17 +3468,16 @@
         <v>7</v>
       </c>
       <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17">
-        <f t="shared" si="1"/>
+      <c r="G9" s="17">
+        <f>SUM(D9:F9)</f>
         <v>14.5</v>
       </c>
-      <c r="I9" s="17">
-        <f t="shared" si="2"/>
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H9" s="26">
+        <f t="shared" ref="H7:H40" si="2">G9/3</f>
+        <v>4.833333333333333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3498,17 +3495,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17">
-        <f t="shared" si="1"/>
+      <c r="G10" s="17">
+        <f>SUM(D10:F10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="17">
+      <c r="H10" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3526,17 +3522,16 @@
         <v>7</v>
       </c>
       <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17">
-        <f t="shared" si="1"/>
+      <c r="G11" s="17">
+        <f>SUM(D11:F11)</f>
         <v>13.5</v>
       </c>
-      <c r="I11" s="17">
-        <f t="shared" si="2"/>
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H11" s="26">
+        <f t="shared" si="2"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3554,17 +3549,16 @@
         <v>7</v>
       </c>
       <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17">
-        <f t="shared" si="1"/>
+      <c r="G12" s="17">
+        <f>SUM(D12:F12)</f>
         <v>13.5</v>
       </c>
-      <c r="I12" s="17">
-        <f t="shared" si="2"/>
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H12" s="26">
+        <f t="shared" si="2"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3582,17 +3576,16 @@
         <v>6</v>
       </c>
       <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17">
-        <f t="shared" si="1"/>
+      <c r="G13" s="17">
+        <f>SUM(D13:F13)</f>
         <v>12.5</v>
       </c>
-      <c r="I13" s="17">
-        <f t="shared" si="2"/>
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H13" s="26">
+        <f t="shared" si="2"/>
+        <v>4.166666666666667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3610,17 +3603,16 @@
         <v>6</v>
       </c>
       <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17">
-        <f t="shared" si="1"/>
+      <c r="G14" s="17">
+        <f>SUM(D14:F14)</f>
         <v>13</v>
       </c>
-      <c r="I14" s="17">
-        <f t="shared" si="2"/>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H14" s="26">
+        <f t="shared" si="2"/>
+        <v>4.333333333333333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -3638,17 +3630,16 @@
         <v>6</v>
       </c>
       <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17">
-        <f t="shared" si="1"/>
+      <c r="G15" s="17">
+        <f>SUM(D15:F15)</f>
         <v>11</v>
       </c>
-      <c r="I15" s="17">
-        <f t="shared" si="2"/>
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H15" s="26">
+        <f t="shared" si="2"/>
+        <v>3.6666666666666665</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -3666,17 +3657,16 @@
         <v>7.5</v>
       </c>
       <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17">
-        <f t="shared" si="1"/>
+      <c r="G16" s="17">
+        <f>SUM(D16:F16)</f>
         <v>15</v>
       </c>
-      <c r="I16" s="17">
-        <f t="shared" si="2"/>
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H16" s="26">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -3694,17 +3684,16 @@
         <v>3.25</v>
       </c>
       <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17">
-        <f t="shared" si="1"/>
+      <c r="G17" s="17">
+        <f>SUM(D17:F17)</f>
         <v>8.75</v>
       </c>
-      <c r="I17" s="17">
-        <f t="shared" si="2"/>
-        <v>4.375</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H17" s="26">
+        <f t="shared" si="2"/>
+        <v>2.9166666666666665</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -3722,17 +3711,16 @@
         <v>6</v>
       </c>
       <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17">
-        <f t="shared" si="1"/>
+      <c r="G18" s="17">
+        <f>SUM(D18:F18)</f>
         <v>12.5</v>
       </c>
-      <c r="I18" s="17">
-        <f t="shared" si="2"/>
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H18" s="26">
+        <f t="shared" si="2"/>
+        <v>4.166666666666667</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -3750,17 +3738,16 @@
         <v>6.5</v>
       </c>
       <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17">
-        <f t="shared" si="1"/>
+      <c r="G19" s="17">
+        <f>SUM(D19:F19)</f>
         <v>13</v>
       </c>
-      <c r="I19" s="17">
-        <f t="shared" si="2"/>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="26">
+        <f t="shared" si="2"/>
+        <v>4.333333333333333</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -3778,17 +3765,16 @@
         <v>5.5</v>
       </c>
       <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17">
-        <f t="shared" si="1"/>
+      <c r="G20" s="17">
+        <f>SUM(D20:F20)</f>
         <v>11.5</v>
       </c>
-      <c r="I20" s="17">
-        <f t="shared" si="2"/>
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H20" s="26">
+        <f t="shared" si="2"/>
+        <v>3.8333333333333335</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3806,17 +3792,16 @@
         <v>7</v>
       </c>
       <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17">
-        <f t="shared" si="1"/>
+      <c r="G21" s="17">
+        <f>SUM(D21:F21)</f>
         <v>13</v>
       </c>
-      <c r="I21" s="17">
-        <f t="shared" si="2"/>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H21" s="26">
+        <f t="shared" si="2"/>
+        <v>4.333333333333333</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3834,17 +3819,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17">
-        <f t="shared" si="1"/>
+      <c r="G22" s="17">
+        <f>SUM(D22:F22)</f>
         <v>6.5</v>
       </c>
-      <c r="I22" s="17">
-        <f t="shared" si="2"/>
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H22" s="26">
+        <f t="shared" si="2"/>
+        <v>2.1666666666666665</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -3862,17 +3846,16 @@
         <v>7</v>
       </c>
       <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17">
-        <f t="shared" si="1"/>
+      <c r="G23" s="17">
+        <f>SUM(D23:F23)</f>
         <v>14</v>
       </c>
-      <c r="I23" s="17">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H23" s="26">
+        <f t="shared" si="2"/>
+        <v>4.666666666666667</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -3890,17 +3873,16 @@
         <v>6.5</v>
       </c>
       <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17">
-        <f t="shared" si="1"/>
+      <c r="G24" s="17">
+        <f>SUM(D24:F24)</f>
         <v>13</v>
       </c>
-      <c r="I24" s="17">
-        <f t="shared" si="2"/>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H24" s="26">
+        <f t="shared" si="2"/>
+        <v>4.333333333333333</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -3918,17 +3900,16 @@
         <v>3.5</v>
       </c>
       <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17">
-        <f t="shared" si="1"/>
+      <c r="G25" s="17">
+        <f>SUM(D25:F25)</f>
         <v>9.5</v>
       </c>
-      <c r="I25" s="17">
-        <f t="shared" si="2"/>
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H25" s="26">
+        <f t="shared" si="2"/>
+        <v>3.1666666666666665</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -3946,17 +3927,16 @@
         <v>7</v>
       </c>
       <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17">
-        <f t="shared" si="1"/>
+      <c r="G26" s="17">
+        <f>SUM(D26:F26)</f>
         <v>14.5</v>
       </c>
-      <c r="I26" s="17">
-        <f t="shared" si="2"/>
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H26" s="26">
+        <f t="shared" si="2"/>
+        <v>4.833333333333333</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3974,17 +3954,16 @@
         <v>6</v>
       </c>
       <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17">
-        <f t="shared" si="1"/>
+      <c r="G27" s="17">
+        <f>SUM(D27:F27)</f>
         <v>12</v>
       </c>
-      <c r="I27" s="17">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H27" s="26">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -4002,17 +3981,16 @@
         <v>7</v>
       </c>
       <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17">
-        <f t="shared" si="1"/>
+      <c r="G28" s="17">
+        <f>SUM(D28:F28)</f>
         <v>14</v>
       </c>
-      <c r="I28" s="17">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H28" s="26">
+        <f t="shared" si="2"/>
+        <v>4.666666666666667</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -4030,17 +4008,16 @@
         <v>7</v>
       </c>
       <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17">
-        <f t="shared" si="1"/>
+      <c r="G29" s="17">
+        <f>SUM(D29:F29)</f>
         <v>14</v>
       </c>
-      <c r="I29" s="17">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H29" s="26">
+        <f t="shared" si="2"/>
+        <v>4.666666666666667</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -4058,17 +4035,16 @@
         <v>7</v>
       </c>
       <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17">
-        <f t="shared" si="1"/>
+      <c r="G30" s="17">
+        <f>SUM(D30:F30)</f>
         <v>14</v>
       </c>
-      <c r="I30" s="17">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H30" s="26">
+        <f t="shared" si="2"/>
+        <v>4.666666666666667</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -4086,17 +4062,16 @@
         <v>7</v>
       </c>
       <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17">
-        <f t="shared" si="1"/>
+      <c r="G31" s="17">
+        <f>SUM(D31:F31)</f>
         <v>14</v>
       </c>
-      <c r="I31" s="17">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H31" s="26">
+        <f t="shared" si="2"/>
+        <v>4.666666666666667</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -4114,17 +4089,16 @@
         <v>7</v>
       </c>
       <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="17">
-        <f t="shared" si="1"/>
+      <c r="G32" s="17">
+        <f>SUM(D32:F32)</f>
         <v>13.5</v>
       </c>
-      <c r="I32" s="17">
-        <f t="shared" si="2"/>
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H32" s="26">
+        <f t="shared" si="2"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -4142,17 +4116,16 @@
         <v>7</v>
       </c>
       <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="17">
-        <f t="shared" si="1"/>
+      <c r="G33" s="17">
+        <f>SUM(D33:F33)</f>
         <v>14</v>
       </c>
-      <c r="I33" s="17">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H33" s="26">
+        <f t="shared" si="2"/>
+        <v>4.666666666666667</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -4170,17 +4143,16 @@
         <v>7.5</v>
       </c>
       <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="17">
-        <f t="shared" si="1"/>
+      <c r="G34" s="17">
+        <f>SUM(D34:F34)</f>
         <v>14.5</v>
       </c>
-      <c r="I34" s="17">
-        <f t="shared" si="2"/>
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H34" s="26">
+        <f t="shared" si="2"/>
+        <v>4.833333333333333</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -4198,17 +4170,16 @@
         <v>6.5</v>
       </c>
       <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="17">
-        <f t="shared" si="1"/>
+      <c r="G35" s="17">
+        <f>SUM(D35:F35)</f>
         <v>10.25</v>
       </c>
-      <c r="I35" s="17">
-        <f t="shared" si="2"/>
-        <v>5.125</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H35" s="26">
+        <f t="shared" si="2"/>
+        <v>3.4166666666666665</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -4226,17 +4197,16 @@
         <v>7</v>
       </c>
       <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="17">
-        <f t="shared" si="1"/>
+      <c r="G36" s="17">
+        <f>SUM(D36:F36)</f>
         <v>13.5</v>
       </c>
-      <c r="I36" s="17">
-        <f t="shared" si="2"/>
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H36" s="26">
+        <f t="shared" si="2"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -4254,17 +4224,16 @@
         <v>6.5</v>
       </c>
       <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="17">
-        <f t="shared" si="1"/>
+      <c r="G37" s="17">
+        <f>SUM(D37:F37)</f>
         <v>13</v>
       </c>
-      <c r="I37" s="17">
-        <f t="shared" si="2"/>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H37" s="26">
+        <f t="shared" si="2"/>
+        <v>4.333333333333333</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -4282,105 +4251,74 @@
         <v>0</v>
       </c>
       <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="17">
-        <f t="shared" si="1"/>
+      <c r="G38" s="17">
+        <f>SUM(D38:F38)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="17">
+      <c r="H38" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B39" s="1">
-        <v>25010901040</v>
+        <v>24010901023</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D39" s="20">
-        <v>0</v>
-      </c>
-      <c r="E39" s="20">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="D39" s="22">
+        <v>6</v>
+      </c>
+      <c r="E39" s="22">
+        <v>3.5</v>
       </c>
       <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G39" s="17">
+        <f>SUM(D39:F39)</f>
+        <v>9.5</v>
+      </c>
+      <c r="H39" s="26">
+        <f t="shared" si="2"/>
+        <v>3.1666666666666665</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B40" s="1">
-        <v>24010901023</v>
+        <v>24010901033</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" s="22">
-        <v>6</v>
-      </c>
-      <c r="E40" s="22">
+        <v>38</v>
+      </c>
+      <c r="D40" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="E40" s="1">
         <v>3.5</v>
       </c>
       <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="17">
-        <f t="shared" si="1"/>
-        <v>9.5</v>
-      </c>
-      <c r="I40" s="17">
-        <f t="shared" si="2"/>
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="B41" s="1">
-        <v>24010901033</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="E41" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="17">
-        <f t="shared" si="1"/>
+      <c r="G40" s="17">
+        <f>SUM(D40:F40)</f>
         <v>10</v>
       </c>
-      <c r="I41" s="17">
-        <f t="shared" si="2"/>
-        <v>5</v>
+      <c r="H40" s="26">
+        <f t="shared" si="2"/>
+        <v>3.3333333333333335</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I3" xr:uid="{2CB2915B-7E74-40B0-9D48-A1940F1D0007}"/>
+  <autoFilter ref="A3:H3" xr:uid="{2CB2915B-7E74-40B0-9D48-A1940F1D0007}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="H1:I2"/>
+    <mergeCell ref="G1:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DCE 2-1/Regular Assessment DCE 2-1.xlsx
+++ b/DCE 2-1/Regular Assessment DCE 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\DCE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0B0A50-226F-4189-961A-7D5892AB17B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C5650B-3168-4B41-ACC0-4B156EC23EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="55">
   <si>
     <t>SL</t>
   </si>
@@ -452,12 +452,6 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -465,6 +459,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -846,14 +846,16 @@
     <col min="12" max="12" width="32.33203125" style="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="32.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="32.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="20.77734375" style="7"/>
+    <col min="15" max="15" width="32.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.88671875" style="7" customWidth="1"/>
+    <col min="17" max="16384" width="20.77734375" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="23"/>
+      <c r="B1" s="26"/>
       <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
@@ -1016,7 +1018,9 @@
       <c r="N3" s="13">
         <v>46286</v>
       </c>
-      <c r="O3" s="13"/>
+      <c r="O3" s="13">
+        <v>46287</v>
+      </c>
       <c r="P3" s="13"/>
       <c r="Q3" s="13"/>
       <c r="R3" s="13"/>
@@ -1040,11 +1044,11 @@
       </c>
       <c r="D4" s="15">
         <f t="shared" ref="D4:D40" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
-        <v>0.77777777777777779</v>
+        <v>0.8</v>
       </c>
       <c r="E4" s="1" cm="1">
         <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>45</v>
@@ -1073,7 +1077,9 @@
       <c r="N4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O4" s="1"/>
+      <c r="O4" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
@@ -1098,11 +1104,11 @@
       </c>
       <c r="D5" s="15">
         <f t="shared" si="1"/>
-        <v>0.77777777777777779</v>
+        <v>0.8</v>
       </c>
       <c r="E5" s="1" cm="1">
         <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,7.5,D5&gt;=80%,6,D5&gt;=70%,4.5,D5&gt;=60%,3,D5&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>45</v>
@@ -1131,7 +1137,9 @@
       <c r="N5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O5" s="1"/>
+      <c r="O5" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
@@ -1156,11 +1164,11 @@
       </c>
       <c r="D6" s="15">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E6" s="1" cm="1">
         <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>45</v>
@@ -1189,7 +1197,9 @@
       <c r="N6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="1"/>
+      <c r="O6" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
@@ -1214,11 +1224,11 @@
       </c>
       <c r="D7" s="15">
         <f t="shared" si="1"/>
-        <v>0.77777777777777779</v>
+        <v>0.8</v>
       </c>
       <c r="E7" s="1" cm="1">
         <f t="array" ref="E7">_xlfn.IFS(D7&gt;=90%,7.5,D7&gt;=80%,6,D7&gt;=70%,4.5,D7&gt;=60%,3,D7&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>45</v>
@@ -1247,7 +1257,9 @@
       <c r="N7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O7" s="1"/>
+      <c r="O7" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
@@ -1272,11 +1284,11 @@
       </c>
       <c r="D8" s="15">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E8" s="1" cm="1">
         <f t="array" ref="E8">_xlfn.IFS(D8&gt;=90%,7.5,D8&gt;=80%,6,D8&gt;=70%,4.5,D8&gt;=60%,3,D8&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>45</v>
@@ -1305,7 +1317,9 @@
       <c r="N8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O8" s="1"/>
+      <c r="O8" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
@@ -1330,7 +1344,7 @@
       </c>
       <c r="D9" s="15">
         <f t="shared" si="1"/>
-        <v>0.77777777777777779</v>
+        <v>0.7</v>
       </c>
       <c r="E9" s="1" cm="1">
         <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
@@ -1363,7 +1377,9 @@
       <c r="N9" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O9" s="1"/>
+      <c r="O9" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
@@ -1388,7 +1404,7 @@
       </c>
       <c r="D10" s="15">
         <f t="shared" si="1"/>
-        <v>0.22222222222222221</v>
+        <v>0.3</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
@@ -1421,7 +1437,9 @@
       <c r="N10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O10" s="1"/>
+      <c r="O10" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
@@ -1446,11 +1464,11 @@
       </c>
       <c r="D11" s="15">
         <f t="shared" si="1"/>
-        <v>0.77777777777777779</v>
+        <v>0.8</v>
       </c>
       <c r="E11" s="1" cm="1">
         <f t="array" ref="E11">_xlfn.IFS(D11&gt;=90%,7.5,D11&gt;=80%,6,D11&gt;=70%,4.5,D11&gt;=60%,3,D11&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>45</v>
@@ -1479,7 +1497,9 @@
       <c r="N11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O11" s="1"/>
+      <c r="O11" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
@@ -1537,7 +1557,9 @@
       <c r="N12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O12" s="1"/>
+      <c r="O12" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -1595,7 +1617,9 @@
       <c r="N13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O13" s="1"/>
+      <c r="O13" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
@@ -1620,11 +1644,11 @@
       </c>
       <c r="D14" s="15">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E14" s="1" cm="1">
         <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>45</v>
@@ -1653,7 +1677,9 @@
       <c r="N14" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O14" s="1"/>
+      <c r="O14" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
@@ -1711,7 +1737,9 @@
       <c r="N15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O15" s="1"/>
+      <c r="O15" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
@@ -1769,7 +1797,9 @@
       <c r="N16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O16" s="1"/>
+      <c r="O16" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
@@ -1794,11 +1824,11 @@
       </c>
       <c r="D17" s="15">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E17" s="1" cm="1">
         <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>45</v>
@@ -1827,7 +1857,9 @@
       <c r="N17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O17" s="1"/>
+      <c r="O17" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
@@ -1852,11 +1884,11 @@
       </c>
       <c r="D18" s="15">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E18" s="1" cm="1">
         <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,7.5,D18&gt;=80%,6,D18&gt;=70%,4.5,D18&gt;=60%,3,D18&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>45</v>
@@ -1885,7 +1917,9 @@
       <c r="N18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O18" s="1"/>
+      <c r="O18" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
@@ -1910,11 +1944,11 @@
       </c>
       <c r="D19" s="15">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E19" s="1" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>45</v>
@@ -1943,7 +1977,9 @@
       <c r="N19" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O19" s="1"/>
+      <c r="O19" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
@@ -1968,11 +2004,11 @@
       </c>
       <c r="D20" s="15">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E20" s="1" cm="1">
         <f t="array" ref="E20">_xlfn.IFS(D20&gt;=90%,7.5,D20&gt;=80%,6,D20&gt;=70%,4.5,D20&gt;=60%,3,D20&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>45</v>
@@ -2001,7 +2037,9 @@
       <c r="N20" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O20" s="1"/>
+      <c r="O20" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
@@ -2026,11 +2064,11 @@
       </c>
       <c r="D21" s="15">
         <f t="shared" si="1"/>
-        <v>0.77777777777777779</v>
+        <v>0.8</v>
       </c>
       <c r="E21" s="1" cm="1">
         <f t="array" ref="E21">_xlfn.IFS(D21&gt;=90%,7.5,D21&gt;=80%,6,D21&gt;=70%,4.5,D21&gt;=60%,3,D21&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>43</v>
@@ -2059,7 +2097,9 @@
       <c r="N21" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O21" s="1"/>
+      <c r="O21" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
@@ -2117,7 +2157,9 @@
       <c r="N22" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O22" s="1"/>
+      <c r="O22" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
@@ -2142,11 +2184,11 @@
       </c>
       <c r="D23" s="15">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E23" s="1" cm="1">
         <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>45</v>
@@ -2175,7 +2217,9 @@
       <c r="N23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O23" s="1"/>
+      <c r="O23" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
@@ -2200,11 +2244,11 @@
       </c>
       <c r="D24" s="15">
         <f t="shared" si="1"/>
-        <v>0.77777777777777779</v>
+        <v>0.8</v>
       </c>
       <c r="E24" s="1" cm="1">
         <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>45</v>
@@ -2233,7 +2277,9 @@
       <c r="N24" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O24" s="1"/>
+      <c r="O24" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
@@ -2258,11 +2304,11 @@
       </c>
       <c r="D25" s="15">
         <f t="shared" si="1"/>
-        <v>0.77777777777777779</v>
+        <v>0.8</v>
       </c>
       <c r="E25" s="1" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>43</v>
@@ -2291,7 +2337,9 @@
       <c r="N25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O25" s="1"/>
+      <c r="O25" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
@@ -2349,7 +2397,9 @@
       <c r="N26" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O26" s="1"/>
+      <c r="O26" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
@@ -2374,7 +2424,7 @@
       </c>
       <c r="D27" s="15">
         <f t="shared" si="1"/>
-        <v>0.77777777777777779</v>
+        <v>0.7</v>
       </c>
       <c r="E27" s="1" cm="1">
         <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,7.5,D27&gt;=80%,6,D27&gt;=70%,4.5,D27&gt;=60%,3,D27&lt;60%,0)</f>
@@ -2407,7 +2457,9 @@
       <c r="N27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O27" s="1"/>
+      <c r="O27" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
@@ -2465,7 +2517,9 @@
       <c r="N28" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O28" s="1"/>
+      <c r="O28" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
@@ -2490,11 +2544,11 @@
       </c>
       <c r="D29" s="15">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E29" s="1" cm="1">
         <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>45</v>
@@ -2523,7 +2577,9 @@
       <c r="N29" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O29" s="1"/>
+      <c r="O29" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
@@ -2548,11 +2604,11 @@
       </c>
       <c r="D30" s="15">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.7</v>
       </c>
       <c r="E30" s="1" cm="1">
         <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>45</v>
@@ -2581,7 +2637,9 @@
       <c r="N30" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O30" s="1"/>
+      <c r="O30" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
@@ -2639,7 +2697,9 @@
       <c r="N31" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O31" s="1"/>
+      <c r="O31" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
@@ -2664,11 +2724,11 @@
       </c>
       <c r="D32" s="15">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E32" s="1" cm="1">
         <f t="array" ref="E32">_xlfn.IFS(D32&gt;=90%,7.5,D32&gt;=80%,6,D32&gt;=70%,4.5,D32&gt;=60%,3,D32&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>45</v>
@@ -2697,7 +2757,9 @@
       <c r="N32" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O32" s="1"/>
+      <c r="O32" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
@@ -2755,7 +2817,9 @@
       <c r="N33" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O33" s="1"/>
+      <c r="O33" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
@@ -2813,7 +2877,9 @@
       <c r="N34" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O34" s="1"/>
+      <c r="O34" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
@@ -2838,11 +2904,11 @@
       </c>
       <c r="D35" s="15">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E35" s="1" cm="1">
         <f t="array" ref="E35">_xlfn.IFS(D35&gt;=90%,7.5,D35&gt;=80%,6,D35&gt;=70%,4.5,D35&gt;=60%,3,D35&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>45</v>
@@ -2871,7 +2937,9 @@
       <c r="N35" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O35" s="1"/>
+      <c r="O35" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
@@ -2896,11 +2964,11 @@
       </c>
       <c r="D36" s="15">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E36" s="1" cm="1">
         <f t="array" ref="E36">_xlfn.IFS(D36&gt;=90%,7.5,D36&gt;=80%,6,D36&gt;=70%,4.5,D36&gt;=60%,3,D36&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>45</v>
@@ -2929,7 +2997,9 @@
       <c r="N36" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O36" s="1"/>
+      <c r="O36" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
@@ -2987,7 +3057,9 @@
       <c r="N37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O37" s="1"/>
+      <c r="O37" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
@@ -3012,7 +3084,7 @@
       </c>
       <c r="D38" s="15">
         <f t="shared" si="1"/>
-        <v>0.44444444444444442</v>
+        <v>0.5</v>
       </c>
       <c r="E38" s="1" cm="1">
         <f t="array" ref="E38">_xlfn.IFS(D38&gt;=90%,7.5,D38&gt;=80%,6,D38&gt;=70%,4.5,D38&gt;=60%,3,D38&lt;60%,0)</f>
@@ -3045,7 +3117,9 @@
       <c r="N38" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O38" s="1"/>
+      <c r="O38" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
@@ -3070,11 +3144,11 @@
       </c>
       <c r="D39" s="15">
         <f t="shared" si="1"/>
-        <v>0.55555555555555558</v>
+        <v>0.6</v>
       </c>
       <c r="E39" s="1" cm="1">
         <f t="array" ref="E39">_xlfn.IFS(D39&gt;=90%,7.5,D39&gt;=80%,6,D39&gt;=70%,4.5,D39&gt;=60%,3,D39&lt;60%,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>45</v>
@@ -3103,7 +3177,9 @@
       <c r="N39" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O39" s="1"/>
+      <c r="O39" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
@@ -3128,7 +3204,7 @@
       </c>
       <c r="D40" s="15">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.6</v>
       </c>
       <c r="E40" s="1" cm="1">
         <f t="array" ref="E40">_xlfn.IFS(D40&gt;=90%,7.5,D40&gt;=80%,6,D40&gt;=70%,4.5,D40&gt;=60%,3,D40&lt;60%,0)</f>
@@ -3161,7 +3237,9 @@
       <c r="N40" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O40" s="1"/>
+      <c r="O40" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
@@ -3240,15 +3318,15 @@
     <col min="5" max="5" width="28.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="31" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.21875" style="25" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="20.77734375" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="23"/>
+      <c r="B1" s="26"/>
       <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
@@ -3261,10 +3339,10 @@
       <c r="F1" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="24"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -3286,8 +3364,8 @@
       <c r="F2" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -3309,10 +3387,10 @@
         <v>7.5</v>
       </c>
       <c r="G3" s="16">
-        <f>SUM(D3:F3)</f>
+        <f t="shared" ref="G3:G40" si="0">SUM(D3:F3)</f>
         <v>22.5</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="23">
         <v>7.5</v>
       </c>
     </row>
@@ -3334,17 +3412,17 @@
       </c>
       <c r="F4" s="17"/>
       <c r="G4" s="17">
-        <f>SUM(D4:F4)</f>
+        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="24">
         <f>G4/3</f>
         <v>4.166666666666667</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <f t="shared" ref="A5:A40" si="0">A4+1</f>
+        <f t="shared" ref="A5:A40" si="1">A4+1</f>
         <v>2</v>
       </c>
       <c r="B5" s="1">
@@ -3361,17 +3439,17 @@
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="17">
-        <f>SUM(D5:F5)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H5" s="26">
-        <f t="shared" ref="H5:H8" si="1">G5/3</f>
+      <c r="H5" s="24">
+        <f t="shared" ref="H5:H8" si="2">G5/3</f>
         <v>2.3333333333333335</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="B6" s="1">
@@ -3388,17 +3466,17 @@
       </c>
       <c r="F6" s="17"/>
       <c r="G6" s="17">
-        <f>SUM(D6:F6)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="H6" s="26">
-        <f t="shared" si="1"/>
+      <c r="H6" s="24">
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="B7" s="1">
@@ -3415,17 +3493,17 @@
       </c>
       <c r="F7" s="17"/>
       <c r="G7" s="17">
-        <f>SUM(D7:F7)</f>
+        <f t="shared" si="0"/>
         <v>10.25</v>
       </c>
-      <c r="H7" s="26">
-        <f t="shared" si="1"/>
+      <c r="H7" s="24">
+        <f t="shared" si="2"/>
         <v>3.4166666666666665</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="B8" s="1">
@@ -3442,17 +3520,17 @@
       </c>
       <c r="F8" s="17"/>
       <c r="G8" s="17">
-        <f>SUM(D8:F8)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="26">
-        <f t="shared" si="1"/>
+      <c r="H8" s="24">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="B9" s="1">
@@ -3469,17 +3547,17 @@
       </c>
       <c r="F9" s="17"/>
       <c r="G9" s="17">
-        <f>SUM(D9:F9)</f>
+        <f t="shared" si="0"/>
         <v>14.5</v>
       </c>
-      <c r="H9" s="26">
-        <f t="shared" ref="H7:H40" si="2">G9/3</f>
+      <c r="H9" s="24">
+        <f t="shared" ref="H9:H40" si="3">G9/3</f>
         <v>4.833333333333333</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="B10" s="1">
@@ -3496,17 +3574,17 @@
       </c>
       <c r="F10" s="17"/>
       <c r="G10" s="17">
-        <f>SUM(D10:F10)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="26">
-        <f t="shared" si="2"/>
+      <c r="H10" s="24">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="B11" s="1">
@@ -3523,17 +3601,17 @@
       </c>
       <c r="F11" s="17"/>
       <c r="G11" s="17">
-        <f>SUM(D11:F11)</f>
+        <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
-      <c r="H11" s="26">
-        <f t="shared" si="2"/>
+      <c r="H11" s="24">
+        <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="B12" s="1">
@@ -3550,17 +3628,17 @@
       </c>
       <c r="F12" s="17"/>
       <c r="G12" s="17">
-        <f>SUM(D12:F12)</f>
+        <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
-      <c r="H12" s="26">
-        <f t="shared" si="2"/>
+      <c r="H12" s="24">
+        <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="B13" s="1">
@@ -3577,17 +3655,17 @@
       </c>
       <c r="F13" s="17"/>
       <c r="G13" s="17">
-        <f>SUM(D13:F13)</f>
+        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
-      <c r="H13" s="26">
-        <f t="shared" si="2"/>
+      <c r="H13" s="24">
+        <f t="shared" si="3"/>
         <v>4.166666666666667</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="B14" s="1">
@@ -3604,17 +3682,17 @@
       </c>
       <c r="F14" s="17"/>
       <c r="G14" s="17">
-        <f>SUM(D14:F14)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="H14" s="26">
-        <f t="shared" si="2"/>
+      <c r="H14" s="24">
+        <f t="shared" si="3"/>
         <v>4.333333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="B15" s="1">
@@ -3631,17 +3709,17 @@
       </c>
       <c r="F15" s="17"/>
       <c r="G15" s="17">
-        <f>SUM(D15:F15)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="H15" s="26">
-        <f t="shared" si="2"/>
+      <c r="H15" s="24">
+        <f t="shared" si="3"/>
         <v>3.6666666666666665</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="B16" s="1">
@@ -3658,17 +3736,17 @@
       </c>
       <c r="F16" s="17"/>
       <c r="G16" s="17">
-        <f>SUM(D16:F16)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="H16" s="26">
-        <f t="shared" si="2"/>
+      <c r="H16" s="24">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="B17" s="1">
@@ -3685,17 +3763,17 @@
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="17">
-        <f>SUM(D17:F17)</f>
+        <f t="shared" si="0"/>
         <v>8.75</v>
       </c>
-      <c r="H17" s="26">
-        <f t="shared" si="2"/>
+      <c r="H17" s="24">
+        <f t="shared" si="3"/>
         <v>2.9166666666666665</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="B18" s="1">
@@ -3712,17 +3790,17 @@
       </c>
       <c r="F18" s="17"/>
       <c r="G18" s="17">
-        <f>SUM(D18:F18)</f>
+        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
-      <c r="H18" s="26">
-        <f t="shared" si="2"/>
+      <c r="H18" s="24">
+        <f t="shared" si="3"/>
         <v>4.166666666666667</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="B19" s="1">
@@ -3739,17 +3817,17 @@
       </c>
       <c r="F19" s="17"/>
       <c r="G19" s="17">
-        <f>SUM(D19:F19)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="H19" s="26">
-        <f t="shared" si="2"/>
+      <c r="H19" s="24">
+        <f t="shared" si="3"/>
         <v>4.333333333333333</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="B20" s="1">
@@ -3766,17 +3844,17 @@
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="17">
-        <f>SUM(D20:F20)</f>
+        <f t="shared" si="0"/>
         <v>11.5</v>
       </c>
-      <c r="H20" s="26">
-        <f t="shared" si="2"/>
+      <c r="H20" s="24">
+        <f t="shared" si="3"/>
         <v>3.8333333333333335</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="B21" s="1">
@@ -3793,17 +3871,17 @@
       </c>
       <c r="F21" s="17"/>
       <c r="G21" s="17">
-        <f>SUM(D21:F21)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="H21" s="26">
-        <f t="shared" si="2"/>
+      <c r="H21" s="24">
+        <f t="shared" si="3"/>
         <v>4.333333333333333</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="B22" s="1">
@@ -3820,17 +3898,17 @@
       </c>
       <c r="F22" s="17"/>
       <c r="G22" s="17">
-        <f>SUM(D22:F22)</f>
+        <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="H22" s="26">
-        <f t="shared" si="2"/>
+      <c r="H22" s="24">
+        <f t="shared" si="3"/>
         <v>2.1666666666666665</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="B23" s="1">
@@ -3847,17 +3925,17 @@
       </c>
       <c r="F23" s="17"/>
       <c r="G23" s="17">
-        <f>SUM(D23:F23)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H23" s="26">
-        <f t="shared" si="2"/>
+      <c r="H23" s="24">
+        <f t="shared" si="3"/>
         <v>4.666666666666667</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="B24" s="1">
@@ -3874,17 +3952,17 @@
       </c>
       <c r="F24" s="17"/>
       <c r="G24" s="17">
-        <f>SUM(D24:F24)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="H24" s="26">
-        <f t="shared" si="2"/>
+      <c r="H24" s="24">
+        <f t="shared" si="3"/>
         <v>4.333333333333333</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="B25" s="1">
@@ -3901,17 +3979,17 @@
       </c>
       <c r="F25" s="17"/>
       <c r="G25" s="17">
-        <f>SUM(D25:F25)</f>
+        <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
-      <c r="H25" s="26">
-        <f t="shared" si="2"/>
+      <c r="H25" s="24">
+        <f t="shared" si="3"/>
         <v>3.1666666666666665</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="B26" s="1">
@@ -3928,17 +4006,17 @@
       </c>
       <c r="F26" s="17"/>
       <c r="G26" s="17">
-        <f>SUM(D26:F26)</f>
+        <f t="shared" si="0"/>
         <v>14.5</v>
       </c>
-      <c r="H26" s="26">
-        <f t="shared" si="2"/>
+      <c r="H26" s="24">
+        <f t="shared" si="3"/>
         <v>4.833333333333333</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="B27" s="1">
@@ -3955,17 +4033,17 @@
       </c>
       <c r="F27" s="17"/>
       <c r="G27" s="17">
-        <f>SUM(D27:F27)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="H27" s="26">
-        <f t="shared" si="2"/>
+      <c r="H27" s="24">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="B28" s="1">
@@ -3982,17 +4060,17 @@
       </c>
       <c r="F28" s="17"/>
       <c r="G28" s="17">
-        <f>SUM(D28:F28)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H28" s="26">
-        <f t="shared" si="2"/>
+      <c r="H28" s="24">
+        <f t="shared" si="3"/>
         <v>4.666666666666667</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="B29" s="1">
@@ -4009,17 +4087,17 @@
       </c>
       <c r="F29" s="17"/>
       <c r="G29" s="17">
-        <f>SUM(D29:F29)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H29" s="26">
-        <f t="shared" si="2"/>
+      <c r="H29" s="24">
+        <f t="shared" si="3"/>
         <v>4.666666666666667</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="B30" s="1">
@@ -4036,17 +4114,17 @@
       </c>
       <c r="F30" s="17"/>
       <c r="G30" s="17">
-        <f>SUM(D30:F30)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H30" s="26">
-        <f t="shared" si="2"/>
+      <c r="H30" s="24">
+        <f t="shared" si="3"/>
         <v>4.666666666666667</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="B31" s="1">
@@ -4063,17 +4141,17 @@
       </c>
       <c r="F31" s="17"/>
       <c r="G31" s="17">
-        <f>SUM(D31:F31)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H31" s="26">
-        <f t="shared" si="2"/>
+      <c r="H31" s="24">
+        <f t="shared" si="3"/>
         <v>4.666666666666667</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="B32" s="1">
@@ -4090,17 +4168,17 @@
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="17">
-        <f>SUM(D32:F32)</f>
+        <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
-      <c r="H32" s="26">
-        <f t="shared" si="2"/>
+      <c r="H32" s="24">
+        <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="B33" s="1">
@@ -4117,17 +4195,17 @@
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="17">
-        <f>SUM(D33:F33)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H33" s="26">
-        <f t="shared" si="2"/>
+      <c r="H33" s="24">
+        <f t="shared" si="3"/>
         <v>4.666666666666667</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="B34" s="1">
@@ -4144,17 +4222,17 @@
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="17">
-        <f>SUM(D34:F34)</f>
+        <f t="shared" si="0"/>
         <v>14.5</v>
       </c>
-      <c r="H34" s="26">
-        <f t="shared" si="2"/>
+      <c r="H34" s="24">
+        <f t="shared" si="3"/>
         <v>4.833333333333333</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="B35" s="1">
@@ -4171,17 +4249,17 @@
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="17">
-        <f>SUM(D35:F35)</f>
+        <f t="shared" si="0"/>
         <v>10.25</v>
       </c>
-      <c r="H35" s="26">
-        <f t="shared" si="2"/>
+      <c r="H35" s="24">
+        <f t="shared" si="3"/>
         <v>3.4166666666666665</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>33</v>
       </c>
       <c r="B36" s="1">
@@ -4198,17 +4276,17 @@
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="17">
-        <f>SUM(D36:F36)</f>
+        <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
-      <c r="H36" s="26">
-        <f t="shared" si="2"/>
+      <c r="H36" s="24">
+        <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="B37" s="1">
@@ -4225,17 +4303,17 @@
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="17">
-        <f>SUM(D37:F37)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="H37" s="26">
-        <f t="shared" si="2"/>
+      <c r="H37" s="24">
+        <f t="shared" si="3"/>
         <v>4.333333333333333</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="B38" s="1">
@@ -4252,17 +4330,17 @@
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="17">
-        <f>SUM(D38:F38)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H38" s="26">
-        <f t="shared" si="2"/>
+      <c r="H38" s="24">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="B39" s="1">
@@ -4279,17 +4357,17 @@
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="17">
-        <f>SUM(D39:F39)</f>
+        <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
-      <c r="H39" s="26">
-        <f t="shared" si="2"/>
+      <c r="H39" s="24">
+        <f t="shared" si="3"/>
         <v>3.1666666666666665</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="B40" s="1">
@@ -4306,11 +4384,11 @@
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="17">
-        <f>SUM(D40:F40)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H40" s="26">
-        <f t="shared" si="2"/>
+      <c r="H40" s="24">
+        <f t="shared" si="3"/>
         <v>3.3333333333333335</v>
       </c>
     </row>

--- a/DCE 2-1/Regular Assessment DCE 2-1.xlsx
+++ b/DCE 2-1/Regular Assessment DCE 2-1.xlsx
@@ -8,17 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\DCE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C5650B-3168-4B41-ACC0-4B156EC23EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8E4587-AA46-4B23-9A7D-16C11E0A4DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DCE 2-1 Attendance" sheetId="3" r:id="rId1"/>
-    <sheet name="Assessment" sheetId="8" r:id="rId2"/>
+    <sheet name="Assignment" sheetId="8" r:id="rId2"/>
+    <sheet name="Class Test" sheetId="9" r:id="rId3"/>
+    <sheet name="Eval." sheetId="10" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!$A$3:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assignment!$A$3:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Class Test'!$A$3:$D$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DCE 2-1 Attendance'!$A$3:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Eval.!$A$3:$D$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="67">
   <si>
     <t>SL</t>
   </si>
@@ -226,6 +230,42 @@
   </si>
   <si>
     <t>Assignment 2</t>
+  </si>
+  <si>
+    <t>Comments on 1st Assignemnt</t>
+  </si>
+  <si>
+    <t>Not Submitted</t>
+  </si>
+  <si>
+    <t>Comments on 2nd Assignemnt</t>
+  </si>
+  <si>
+    <t>Comments on 3rd Assignemnt</t>
+  </si>
+  <si>
+    <t>Drew 1 Figure</t>
+  </si>
+  <si>
+    <t>Omit some actions</t>
+  </si>
+  <si>
+    <t>NOAS</t>
+  </si>
+  <si>
+    <t>Attendance</t>
+  </si>
+  <si>
+    <t>Assignment</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>NOCT</t>
+  </si>
+  <si>
+    <t>BOEV</t>
   </si>
 </sst>
 </file>
@@ -283,7 +323,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -355,8 +395,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -379,12 +431,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -440,9 +529,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -461,10 +547,34 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -830,7 +940,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y43"/>
+  <dimension ref="A1:T43"/>
   <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" style="7" bestFit="1" customWidth="1"/>
@@ -847,15 +957,15 @@
     <col min="13" max="13" width="32.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="32.33203125" style="7" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="32.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.88671875" style="7" customWidth="1"/>
+    <col min="16" max="16" width="32.21875" style="7" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="20.77734375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="26"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
@@ -876,13 +986,8 @@
       <c r="R1" s="11"/>
       <c r="S1" s="11"/>
       <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="11"/>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>40</v>
       </c>
@@ -903,7 +1008,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="12">
-        <f t="shared" ref="H2:Y2" si="0">G2+1</f>
+        <f t="shared" ref="H2:T2" si="0">G2+1</f>
         <v>3</v>
       </c>
       <c r="I2" s="12">
@@ -954,28 +1059,8 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="U2" s="12">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="V2" s="12">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="W2" s="12">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="X2" s="12">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="Y2" s="12">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1021,18 +1106,15 @@
       <c r="O3" s="13">
         <v>46287</v>
       </c>
-      <c r="P3" s="13"/>
+      <c r="P3" s="13">
+        <v>46293</v>
+      </c>
       <c r="Q3" s="13"/>
       <c r="R3" s="13"/>
       <c r="S3" s="13"/>
       <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1043,8 +1125,8 @@
         <v>3</v>
       </c>
       <c r="D4" s="15">
-        <f t="shared" ref="D4:D40" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
-        <v>0.8</v>
+        <f t="shared" ref="D4:D40" si="1">COUNTIF(F4:T4,"P")/(COUNTIF(F4:T4,"P")+COUNTIF(F4:T4,"A"))</f>
+        <v>0.81818181818181823</v>
       </c>
       <c r="E4" s="1" cm="1">
         <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
@@ -1080,18 +1162,15 @@
       <c r="O4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P4" s="1"/>
+      <c r="P4" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A31" si="2">A4+1</f>
         <v>2</v>
@@ -1104,7 +1183,7 @@
       </c>
       <c r="D5" s="15">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="E5" s="1" cm="1">
         <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,7.5,D5&gt;=80%,6,D5&gt;=70%,4.5,D5&gt;=60%,3,D5&lt;60%,0)</f>
@@ -1140,18 +1219,15 @@
       <c r="O5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P5" s="1"/>
+      <c r="P5" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" si="2"/>
         <v>3</v>
@@ -1164,7 +1240,7 @@
       </c>
       <c r="D6" s="15">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E6" s="1" cm="1">
         <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
@@ -1200,18 +1276,15 @@
       <c r="O6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P6" s="1"/>
+      <c r="P6" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -1224,7 +1297,7 @@
       </c>
       <c r="D7" s="15">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="E7" s="1" cm="1">
         <f t="array" ref="E7">_xlfn.IFS(D7&gt;=90%,7.5,D7&gt;=80%,6,D7&gt;=70%,4.5,D7&gt;=60%,3,D7&lt;60%,0)</f>
@@ -1260,18 +1333,15 @@
       <c r="O7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P7" s="1"/>
+      <c r="P7" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -1284,7 +1354,7 @@
       </c>
       <c r="D8" s="15">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E8" s="1" cm="1">
         <f t="array" ref="E8">_xlfn.IFS(D8&gt;=90%,7.5,D8&gt;=80%,6,D8&gt;=70%,4.5,D8&gt;=60%,3,D8&lt;60%,0)</f>
@@ -1320,18 +1390,15 @@
       <c r="O8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P8" s="1"/>
+      <c r="P8" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -1344,7 +1411,7 @@
       </c>
       <c r="D9" s="15">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="E9" s="1" cm="1">
         <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
@@ -1380,19 +1447,16 @@
       <c r="O9" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="P9" s="1"/>
+      <c r="P9" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
@@ -1404,7 +1468,7 @@
       </c>
       <c r="D10" s="15">
         <f t="shared" si="1"/>
-        <v>0.3</v>
+        <v>0.27272727272727271</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
@@ -1440,18 +1504,15 @@
       <c r="O10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P10" s="1"/>
+      <c r="P10" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -1464,7 +1525,7 @@
       </c>
       <c r="D11" s="15">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="E11" s="1" cm="1">
         <f t="array" ref="E11">_xlfn.IFS(D11&gt;=90%,7.5,D11&gt;=80%,6,D11&gt;=70%,4.5,D11&gt;=60%,3,D11&lt;60%,0)</f>
@@ -1500,18 +1561,15 @@
       <c r="O11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -1560,18 +1618,15 @@
       <c r="O12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P12" s="1"/>
+      <c r="P12" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -1620,18 +1675,15 @@
       <c r="O13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P13" s="1"/>
+      <c r="P13" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="1"/>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="1"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -1644,7 +1696,7 @@
       </c>
       <c r="D14" s="15">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E14" s="1" cm="1">
         <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
@@ -1680,18 +1732,15 @@
       <c r="O14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P14" s="1"/>
+      <c r="P14" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -1740,18 +1789,15 @@
       <c r="O15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P15" s="1"/>
+      <c r="P15" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -1764,7 +1810,7 @@
       </c>
       <c r="D16" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E16" s="1" cm="1">
         <f t="array" ref="E16">_xlfn.IFS(D16&gt;=90%,7.5,D16&gt;=80%,6,D16&gt;=70%,4.5,D16&gt;=60%,3,D16&lt;60%,0)</f>
@@ -1800,18 +1846,15 @@
       <c r="O16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P16" s="1"/>
+      <c r="P16" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -1824,11 +1867,11 @@
       </c>
       <c r="D17" s="15">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="E17" s="1" cm="1">
         <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>45</v>
@@ -1860,18 +1903,15 @@
       <c r="O17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P17" s="1"/>
+      <c r="P17" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -1884,7 +1924,7 @@
       </c>
       <c r="D18" s="15">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E18" s="1" cm="1">
         <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,7.5,D18&gt;=80%,6,D18&gt;=70%,4.5,D18&gt;=60%,3,D18&lt;60%,0)</f>
@@ -1920,18 +1960,15 @@
       <c r="O18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P18" s="1"/>
+      <c r="P18" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -1944,7 +1981,7 @@
       </c>
       <c r="D19" s="15">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E19" s="1" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
@@ -1980,18 +2017,15 @@
       <c r="O19" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P19" s="1"/>
+      <c r="P19" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -2004,7 +2038,7 @@
       </c>
       <c r="D20" s="15">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E20" s="1" cm="1">
         <f t="array" ref="E20">_xlfn.IFS(D20&gt;=90%,7.5,D20&gt;=80%,6,D20&gt;=70%,4.5,D20&gt;=60%,3,D20&lt;60%,0)</f>
@@ -2040,18 +2074,15 @@
       <c r="O20" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P20" s="1"/>
+      <c r="P20" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -2064,7 +2095,7 @@
       </c>
       <c r="D21" s="15">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="E21" s="1" cm="1">
         <f t="array" ref="E21">_xlfn.IFS(D21&gt;=90%,7.5,D21&gt;=80%,6,D21&gt;=70%,4.5,D21&gt;=60%,3,D21&lt;60%,0)</f>
@@ -2100,18 +2131,15 @@
       <c r="O21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P21" s="1"/>
+      <c r="P21" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -2160,18 +2188,15 @@
       <c r="O22" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P22" s="1"/>
+      <c r="P22" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -2184,7 +2209,7 @@
       </c>
       <c r="D23" s="15">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E23" s="1" cm="1">
         <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
@@ -2220,18 +2245,15 @@
       <c r="O23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P23" s="1"/>
+      <c r="P23" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="1"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -2244,7 +2266,7 @@
       </c>
       <c r="D24" s="15">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="E24" s="1" cm="1">
         <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
@@ -2280,18 +2302,15 @@
       <c r="O24" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P24" s="1"/>
+      <c r="P24" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -2304,7 +2323,7 @@
       </c>
       <c r="D25" s="15">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="E25" s="1" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
@@ -2340,18 +2359,15 @@
       <c r="O25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P25" s="1"/>
+      <c r="P25" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -2400,18 +2416,15 @@
       <c r="O26" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P26" s="1"/>
+      <c r="P26" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -2424,7 +2437,7 @@
       </c>
       <c r="D27" s="15">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="E27" s="1" cm="1">
         <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,7.5,D27&gt;=80%,6,D27&gt;=70%,4.5,D27&gt;=60%,3,D27&lt;60%,0)</f>
@@ -2460,18 +2473,15 @@
       <c r="O27" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="P27" s="1"/>
+      <c r="P27" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -2520,18 +2530,15 @@
       <c r="O28" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P28" s="1"/>
+      <c r="P28" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -2544,7 +2551,7 @@
       </c>
       <c r="D29" s="15">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E29" s="1" cm="1">
         <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
@@ -2580,18 +2587,15 @@
       <c r="O29" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P29" s="1"/>
+      <c r="P29" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -2604,7 +2608,7 @@
       </c>
       <c r="D30" s="15">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="E30" s="1" cm="1">
         <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
@@ -2640,18 +2644,15 @@
       <c r="O30" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P30" s="1"/>
+      <c r="P30" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -2700,18 +2701,15 @@
       <c r="O31" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P31" s="1"/>
+      <c r="P31" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f t="shared" ref="A32:A40" si="3">A31+1</f>
         <v>29</v>
@@ -2724,11 +2722,11 @@
       </c>
       <c r="D32" s="15">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="E32" s="1" cm="1">
         <f t="array" ref="E32">_xlfn.IFS(D32&gt;=90%,7.5,D32&gt;=80%,6,D32&gt;=70%,4.5,D32&gt;=60%,3,D32&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>45</v>
@@ -2760,18 +2758,15 @@
       <c r="O32" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P32" s="1"/>
+      <c r="P32" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -2820,18 +2815,15 @@
       <c r="O33" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P33" s="1"/>
+      <c r="P33" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
-      <c r="W33" s="1"/>
-      <c r="X33" s="1"/>
-      <c r="Y33" s="1"/>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f t="shared" si="3"/>
         <v>31</v>
@@ -2880,18 +2872,15 @@
       <c r="O34" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P34" s="1"/>
+      <c r="P34" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f t="shared" si="3"/>
         <v>32</v>
@@ -2904,7 +2893,7 @@
       </c>
       <c r="D35" s="15">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E35" s="1" cm="1">
         <f t="array" ref="E35">_xlfn.IFS(D35&gt;=90%,7.5,D35&gt;=80%,6,D35&gt;=70%,4.5,D35&gt;=60%,3,D35&lt;60%,0)</f>
@@ -2940,18 +2929,15 @@
       <c r="O35" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P35" s="1"/>
+      <c r="P35" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f t="shared" si="3"/>
         <v>33</v>
@@ -2964,11 +2950,11 @@
       </c>
       <c r="D36" s="15">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="E36" s="1" cm="1">
         <f t="array" ref="E36">_xlfn.IFS(D36&gt;=90%,7.5,D36&gt;=80%,6,D36&gt;=70%,4.5,D36&gt;=60%,3,D36&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>45</v>
@@ -3000,18 +2986,15 @@
       <c r="O36" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P36" s="1"/>
+      <c r="P36" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
-      <c r="W36" s="1"/>
-      <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f t="shared" si="3"/>
         <v>34</v>
@@ -3060,18 +3043,15 @@
       <c r="O37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P37" s="1"/>
+      <c r="P37" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="1"/>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <f t="shared" si="3"/>
         <v>35</v>
@@ -3084,7 +3064,7 @@
       </c>
       <c r="D38" s="15">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.45454545454545453</v>
       </c>
       <c r="E38" s="1" cm="1">
         <f t="array" ref="E38">_xlfn.IFS(D38&gt;=90%,7.5,D38&gt;=80%,6,D38&gt;=70%,4.5,D38&gt;=60%,3,D38&lt;60%,0)</f>
@@ -3120,18 +3100,15 @@
       <c r="O38" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P38" s="1"/>
+      <c r="P38" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <f t="shared" si="3"/>
         <v>36</v>
@@ -3144,11 +3121,11 @@
       </c>
       <c r="D39" s="15">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="E39" s="1" cm="1">
         <f t="array" ref="E39">_xlfn.IFS(D39&gt;=90%,7.5,D39&gt;=80%,6,D39&gt;=70%,4.5,D39&gt;=60%,3,D39&lt;60%,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>45</v>
@@ -3180,18 +3157,15 @@
       <c r="O39" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P39" s="1"/>
+      <c r="P39" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <f t="shared" si="3"/>
         <v>37</v>
@@ -3204,7 +3178,7 @@
       </c>
       <c r="D40" s="15">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="E40" s="1" cm="1">
         <f t="array" ref="E40">_xlfn.IFS(D40&gt;=90%,7.5,D40&gt;=80%,6,D40&gt;=70%,4.5,D40&gt;=60%,3,D40&lt;60%,0)</f>
@@ -3240,29 +3214,26 @@
       <c r="O40" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="P40" s="1"/>
+      <c r="P40" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1"/>
-      <c r="W40" s="1"/>
-      <c r="X40" s="1"/>
-      <c r="Y40" s="1"/>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="E41" s="7"/>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
       <c r="I41" s="14"/>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
       <c r="I42" s="14"/>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
       <c r="I43" s="14"/>
@@ -3308,7 +3279,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CB2915B-7E74-40B0-9D48-A1940F1D0007}">
-  <dimension ref="A1:H40"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" style="7" bestFit="1" customWidth="1"/>
@@ -3317,16 +3291,18 @@
     <col min="4" max="4" width="25.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="31" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.21875" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="20.77734375" style="7"/>
+    <col min="7" max="7" width="11.44140625" style="7" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" style="24" customWidth="1"/>
+    <col min="9" max="9" width="25.44140625" style="7" customWidth="1"/>
+    <col min="10" max="11" width="27.77734375" style="7" customWidth="1"/>
+    <col min="12" max="16384" width="20.77734375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="26"/>
+      <c r="B1" s="27"/>
       <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
@@ -3339,12 +3315,21 @@
       <c r="F1" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="27"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H1" s="28"/>
+      <c r="I1" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>40</v>
       </c>
@@ -3353,7 +3338,7 @@
         <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>50</v>
@@ -3364,10 +3349,13 @@
       <c r="F2" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-    </row>
-    <row r="3" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+    </row>
+    <row r="3" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -3390,11 +3378,14 @@
         <f t="shared" ref="G3:G40" si="0">SUM(D3:F3)</f>
         <v>22.5</v>
       </c>
-      <c r="H3" s="23">
+      <c r="H3" s="22">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="29"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3407,7 +3398,7 @@
       <c r="D4" s="17">
         <v>6</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="20">
         <v>6.5</v>
       </c>
       <c r="F4" s="17"/>
@@ -3415,12 +3406,15 @@
         <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
-      <c r="H4" s="24">
+      <c r="H4" s="23">
         <f>G4/3</f>
         <v>4.166666666666667</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A40" si="1">A4+1</f>
         <v>2</v>
@@ -3431,10 +3425,10 @@
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="20">
         <v>3.75</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="20">
         <v>3.25</v>
       </c>
       <c r="F5" s="17"/>
@@ -3442,12 +3436,19 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="23">
         <f t="shared" ref="H5:H8" si="2">G5/3</f>
         <v>2.3333333333333335</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -3469,12 +3470,15 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="23">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -3496,12 +3500,17 @@
         <f t="shared" si="0"/>
         <v>10.25</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="23">
         <f t="shared" si="2"/>
         <v>3.4166666666666665</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -3512,23 +3521,26 @@
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="19">
-        <v>0</v>
-      </c>
-      <c r="E8" s="19">
-        <v>0</v>
-      </c>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
       <c r="F8" s="17"/>
       <c r="G8" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -3550,12 +3562,15 @@
         <f t="shared" si="0"/>
         <v>14.5</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="23">
         <f t="shared" ref="H9:H40" si="3">G9/3</f>
         <v>4.833333333333333</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -3566,23 +3581,26 @@
       <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="19">
-        <v>0</v>
-      </c>
-      <c r="E10" s="19">
-        <v>0</v>
-      </c>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
       <c r="F10" s="17"/>
       <c r="G10" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -3604,12 +3622,15 @@
         <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="23">
         <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -3631,12 +3652,15 @@
         <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="23">
         <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -3658,12 +3682,15 @@
         <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="23">
         <f t="shared" si="3"/>
         <v>4.166666666666667</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -3685,12 +3712,15 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="23">
         <f t="shared" si="3"/>
         <v>4.333333333333333</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -3712,12 +3742,17 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="23">
         <f t="shared" si="3"/>
         <v>3.6666666666666665</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -3739,12 +3774,15 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="23">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -3766,12 +3804,19 @@
         <f t="shared" si="0"/>
         <v>8.75</v>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="23">
         <f t="shared" si="3"/>
         <v>2.9166666666666665</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -3785,7 +3830,7 @@
       <c r="D18" s="17">
         <v>6.5</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="20">
         <v>6</v>
       </c>
       <c r="F18" s="17"/>
@@ -3793,12 +3838,15 @@
         <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="23">
         <f t="shared" si="3"/>
         <v>4.166666666666667</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -3812,7 +3860,7 @@
       <c r="D19" s="17">
         <v>6.5</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="20">
         <v>6.5</v>
       </c>
       <c r="F19" s="17"/>
@@ -3820,12 +3868,15 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="H19" s="24">
+      <c r="H19" s="23">
         <f t="shared" si="3"/>
         <v>4.333333333333333</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -3839,7 +3890,7 @@
       <c r="D20" s="17">
         <v>6</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="20">
         <v>5.5</v>
       </c>
       <c r="F20" s="17"/>
@@ -3847,12 +3898,15 @@
         <f t="shared" si="0"/>
         <v>11.5</v>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="23">
         <f t="shared" si="3"/>
         <v>3.8333333333333335</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -3874,12 +3928,15 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="H21" s="24">
+      <c r="H21" s="23">
         <f t="shared" si="3"/>
         <v>4.333333333333333</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -3893,20 +3950,23 @@
       <c r="D22" s="17">
         <v>6.5</v>
       </c>
-      <c r="E22" s="19">
-        <v>0</v>
-      </c>
+      <c r="E22" s="26"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="H22" s="24">
+      <c r="H22" s="23">
         <f t="shared" si="3"/>
         <v>2.1666666666666665</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I22" s="1"/>
+      <c r="J22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -3928,12 +3988,15 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H23" s="24">
+      <c r="H23" s="23">
         <f t="shared" si="3"/>
         <v>4.666666666666667</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -3955,12 +4018,15 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="H24" s="24">
+      <c r="H24" s="23">
         <f t="shared" si="3"/>
         <v>4.333333333333333</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -3982,12 +4048,17 @@
         <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
-      <c r="H25" s="24">
+      <c r="H25" s="23">
         <f t="shared" si="3"/>
         <v>3.1666666666666665</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -4009,12 +4080,15 @@
         <f t="shared" si="0"/>
         <v>14.5</v>
       </c>
-      <c r="H26" s="24">
+      <c r="H26" s="23">
         <f t="shared" si="3"/>
         <v>4.833333333333333</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -4025,10 +4099,10 @@
       <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="20">
         <v>6</v>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="20">
         <v>6</v>
       </c>
       <c r="F27" s="17"/>
@@ -4036,12 +4110,15 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="H27" s="24">
+      <c r="H27" s="23">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -4063,12 +4140,15 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H28" s="24">
+      <c r="H28" s="23">
         <f t="shared" si="3"/>
         <v>4.666666666666667</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -4090,12 +4170,15 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H29" s="24">
+      <c r="H29" s="23">
         <f t="shared" si="3"/>
         <v>4.666666666666667</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -4117,12 +4200,15 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H30" s="24">
+      <c r="H30" s="23">
         <f t="shared" si="3"/>
         <v>4.666666666666667</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -4144,12 +4230,15 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H31" s="24">
+      <c r="H31" s="23">
         <f t="shared" si="3"/>
         <v>4.666666666666667</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -4171,12 +4260,15 @@
         <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
-      <c r="H32" s="24">
+      <c r="H32" s="23">
         <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -4198,12 +4290,15 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H33" s="24">
+      <c r="H33" s="23">
         <f t="shared" si="3"/>
         <v>4.666666666666667</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -4225,12 +4320,15 @@
         <f t="shared" si="0"/>
         <v>14.5</v>
       </c>
-      <c r="H34" s="24">
+      <c r="H34" s="23">
         <f t="shared" si="3"/>
         <v>4.833333333333333</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -4252,12 +4350,17 @@
         <f t="shared" si="0"/>
         <v>10.25</v>
       </c>
-      <c r="H35" s="24">
+      <c r="H35" s="23">
         <f t="shared" si="3"/>
         <v>3.4166666666666665</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -4279,12 +4382,15 @@
         <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
-      <c r="H36" s="24">
+      <c r="H36" s="23">
         <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -4306,12 +4412,15 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="H37" s="24">
+      <c r="H37" s="23">
         <f t="shared" si="3"/>
         <v>4.333333333333333</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -4322,23 +4431,26 @@
       <c r="C38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="20">
-        <v>0</v>
-      </c>
-      <c r="E38" s="20">
-        <v>0</v>
-      </c>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
       <c r="F38" s="1"/>
       <c r="G38" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H38" s="24">
+      <c r="H38" s="23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I38" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K38" s="1"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -4349,10 +4461,10 @@
       <c r="C39" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="21">
         <v>6</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="21">
         <v>3.5</v>
       </c>
       <c r="F39" s="1"/>
@@ -4360,12 +4472,17 @@
         <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
-      <c r="H39" s="24">
+      <c r="H39" s="23">
         <f t="shared" si="3"/>
         <v>3.1666666666666665</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K39" s="1"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -4387,18 +4504,1697 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H40" s="24">
+      <c r="H40" s="23">
         <f t="shared" si="3"/>
         <v>3.3333333333333335</v>
       </c>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K40" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H3" xr:uid="{2CB2915B-7E74-40B0-9D48-A1940F1D0007}"/>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="G1:H2"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="K1:K3"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="55" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D4A7C06-C1C4-4F85-AAC7-96941168A43E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D40"/>
+  <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="20.77734375" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="12"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="3">
+        <f>COUNT(A4:A40)</f>
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>25010901001</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="20"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <f t="shared" ref="A5:A40" si="0">A4+1</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>25010901002</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="20"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>25010901003</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="20"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>25010901004</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="20"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>25010901005</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="20"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>25010901007</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="20"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>25010901009</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="20"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>25010901010</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="20"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>25010901011</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="20"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>25010901012</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="20"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>25010901013</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="20"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>25010901014</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="20"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>25010901015</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="20"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>25010901017</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="20"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="10">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>25010901018</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="20"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B19" s="1">
+        <v>25010901019</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="20"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>25010901020</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="20"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="1">
+        <v>25010901021</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="20"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
+        <v>25010901022</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="20"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="1">
+        <v>25010901023</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="20"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="1">
+        <v>25010901024</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="20"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>25010901025</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="20"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>25010901026</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="20"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="1">
+        <v>25010901027</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="20"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="10">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="1">
+        <v>25010901029</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="20"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="1">
+        <v>25010901030</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="20"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="1">
+        <v>25010901031</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="20"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="1">
+        <v>25010901032</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="20"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="1">
+        <v>25010901033</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="21"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="1">
+        <v>25010901034</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="21"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="1">
+        <v>25010901035</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="21"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="1">
+        <v>25010901036</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="21"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="1">
+        <v>25010901037</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="21"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="1">
+        <v>25010901038</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="21"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="1">
+        <v>25010901039</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="21"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="1">
+        <v>24010901023</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="21"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="1">
+        <v>24010901033</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="21"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:D3" xr:uid="{2CB2915B-7E74-40B0-9D48-A1940F1D0007}"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="55" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{057EB2B6-E7E2-42B8-822F-A3E3956A3253}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.44140625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="19" style="7" customWidth="1"/>
+    <col min="7" max="7" width="21.109375" style="7" customWidth="1"/>
+    <col min="8" max="16384" width="20.77734375" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="3">
+        <f>COUNT(A4:A40)</f>
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="18">
+        <v>7.5</v>
+      </c>
+      <c r="E3" s="18">
+        <v>7.5</v>
+      </c>
+      <c r="F3" s="18">
+        <v>15</v>
+      </c>
+      <c r="G3" s="18">
+        <f>SUM(D3:F3)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>25010901001</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="20">
+        <f>_xlfn.XLOOKUP(B4,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>6</v>
+      </c>
+      <c r="E4" s="33">
+        <f>_xlfn.XLOOKUP(B4,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="F4" s="20">
+        <f>_xlfn.XLOOKUP(B4,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="34">
+        <f>CEILING(SUM(D4:F4),0.5)</f>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <f t="shared" ref="A5:A40" si="0">A4+1</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>25010901002</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="20">
+        <f>_xlfn.XLOOKUP(B5,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>6</v>
+      </c>
+      <c r="E5" s="33">
+        <f>_xlfn.XLOOKUP(B5,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="F5" s="20">
+        <f>_xlfn.XLOOKUP(B5,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="34">
+        <f t="shared" ref="G5:G40" si="1">CEILING(SUM(D5:F5),0.5)</f>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>25010901003</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="20">
+        <f>_xlfn.XLOOKUP(B6,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E6" s="33">
+        <f>_xlfn.XLOOKUP(B6,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4</v>
+      </c>
+      <c r="F6" s="20">
+        <f>_xlfn.XLOOKUP(B6,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="34">
+        <f t="shared" si="1"/>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>25010901004</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="20">
+        <f>_xlfn.XLOOKUP(B7,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>6</v>
+      </c>
+      <c r="E7" s="33">
+        <f>_xlfn.XLOOKUP(B7,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>3.4166666666666665</v>
+      </c>
+      <c r="F7" s="20">
+        <f>_xlfn.XLOOKUP(B7,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="34">
+        <f t="shared" si="1"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>25010901005</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="20">
+        <f>_xlfn.XLOOKUP(B8,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E8" s="33">
+        <f>_xlfn.XLOOKUP(B8,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="20">
+        <f>_xlfn.XLOOKUP(B8,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="34">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>25010901007</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="20">
+        <f>_xlfn.XLOOKUP(B9,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E9" s="33">
+        <f>_xlfn.XLOOKUP(B9,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.833333333333333</v>
+      </c>
+      <c r="F9" s="20">
+        <f>_xlfn.XLOOKUP(B9,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="34">
+        <f t="shared" si="1"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>25010901009</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="20">
+        <f>_xlfn.XLOOKUP(B10,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="33">
+        <f>_xlfn.XLOOKUP(B10,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="20">
+        <f>_xlfn.XLOOKUP(B10,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>25010901010</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="20">
+        <f>_xlfn.XLOOKUP(B11,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>6</v>
+      </c>
+      <c r="E11" s="33">
+        <f>_xlfn.XLOOKUP(B11,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F11" s="20">
+        <f>_xlfn.XLOOKUP(B11,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="34">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>25010901011</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="20">
+        <f>_xlfn.XLOOKUP(B12,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E12" s="33">
+        <f>_xlfn.XLOOKUP(B12,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F12" s="20">
+        <f>_xlfn.XLOOKUP(B12,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="34">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>25010901012</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="20">
+        <f>_xlfn.XLOOKUP(B13,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E13" s="33">
+        <f>_xlfn.XLOOKUP(B13,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="F13" s="20">
+        <f>_xlfn.XLOOKUP(B13,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="34">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>25010901013</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="20">
+        <f>_xlfn.XLOOKUP(B14,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E14" s="33">
+        <f>_xlfn.XLOOKUP(B14,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="F14" s="20">
+        <f>_xlfn.XLOOKUP(B14,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="34">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>25010901014</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="20">
+        <f>_xlfn.XLOOKUP(B15,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E15" s="33">
+        <f>_xlfn.XLOOKUP(B15,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="F15" s="20">
+        <f>_xlfn.XLOOKUP(B15,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="34">
+        <f t="shared" si="1"/>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>25010901015</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="20">
+        <f>_xlfn.XLOOKUP(B16,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E16" s="33">
+        <f>_xlfn.XLOOKUP(B16,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>5</v>
+      </c>
+      <c r="F16" s="20">
+        <f>_xlfn.XLOOKUP(B16,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="34">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>25010901017</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="20">
+        <f>_xlfn.XLOOKUP(B17,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>6</v>
+      </c>
+      <c r="E17" s="33">
+        <f>_xlfn.XLOOKUP(B17,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>2.9166666666666665</v>
+      </c>
+      <c r="F17" s="20">
+        <f>_xlfn.XLOOKUP(B17,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="34">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="10">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>25010901018</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="20">
+        <f>_xlfn.XLOOKUP(B18,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E18" s="33">
+        <f>_xlfn.XLOOKUP(B18,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="F18" s="20">
+        <f>_xlfn.XLOOKUP(B18,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="34">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B19" s="1">
+        <v>25010901019</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="20">
+        <f>_xlfn.XLOOKUP(B19,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E19" s="33">
+        <f>_xlfn.XLOOKUP(B19,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="F19" s="20">
+        <f>_xlfn.XLOOKUP(B19,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="34">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>25010901020</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="20">
+        <f>_xlfn.XLOOKUP(B20,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E20" s="33">
+        <f>_xlfn.XLOOKUP(B20,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="F20" s="20">
+        <f>_xlfn.XLOOKUP(B20,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="34">
+        <f t="shared" si="1"/>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="1">
+        <v>25010901021</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="20">
+        <f>_xlfn.XLOOKUP(B21,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>6</v>
+      </c>
+      <c r="E21" s="33">
+        <f>_xlfn.XLOOKUP(B21,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="F21" s="20">
+        <f>_xlfn.XLOOKUP(B21,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="34">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
+        <v>25010901022</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="20">
+        <f>_xlfn.XLOOKUP(B22,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E22" s="33">
+        <f>_xlfn.XLOOKUP(B22,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="F22" s="20">
+        <f>_xlfn.XLOOKUP(B22,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="34">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="1">
+        <v>25010901023</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="20">
+        <f>_xlfn.XLOOKUP(B23,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E23" s="33">
+        <f>_xlfn.XLOOKUP(B23,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.666666666666667</v>
+      </c>
+      <c r="F23" s="20">
+        <f>_xlfn.XLOOKUP(B23,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="34">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="1">
+        <v>25010901024</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="20">
+        <f>_xlfn.XLOOKUP(B24,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>6</v>
+      </c>
+      <c r="E24" s="33">
+        <f>_xlfn.XLOOKUP(B24,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="F24" s="20">
+        <f>_xlfn.XLOOKUP(B24,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="34">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>25010901025</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="20">
+        <f>_xlfn.XLOOKUP(B25,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>6</v>
+      </c>
+      <c r="E25" s="33">
+        <f>_xlfn.XLOOKUP(B25,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>3.1666666666666665</v>
+      </c>
+      <c r="F25" s="20">
+        <f>_xlfn.XLOOKUP(B25,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="34">
+        <f t="shared" si="1"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>25010901026</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="20">
+        <f>_xlfn.XLOOKUP(B26,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E26" s="33">
+        <f>_xlfn.XLOOKUP(B26,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.833333333333333</v>
+      </c>
+      <c r="F26" s="20">
+        <f>_xlfn.XLOOKUP(B26,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="34">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="1">
+        <v>25010901027</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="20">
+        <f>_xlfn.XLOOKUP(B27,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E27" s="33">
+        <f>_xlfn.XLOOKUP(B27,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4</v>
+      </c>
+      <c r="F27" s="20">
+        <f>_xlfn.XLOOKUP(B27,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="34">
+        <f t="shared" si="1"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="10">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="1">
+        <v>25010901029</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="20">
+        <f>_xlfn.XLOOKUP(B28,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E28" s="33">
+        <f>_xlfn.XLOOKUP(B28,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.666666666666667</v>
+      </c>
+      <c r="F28" s="20">
+        <f>_xlfn.XLOOKUP(B28,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="34">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="1">
+        <v>25010901030</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="20">
+        <f>_xlfn.XLOOKUP(B29,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E29" s="33">
+        <f>_xlfn.XLOOKUP(B29,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.666666666666667</v>
+      </c>
+      <c r="F29" s="20">
+        <f>_xlfn.XLOOKUP(B29,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="34">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="1">
+        <v>25010901031</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="20">
+        <f>_xlfn.XLOOKUP(B30,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E30" s="33">
+        <f>_xlfn.XLOOKUP(B30,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.666666666666667</v>
+      </c>
+      <c r="F30" s="20">
+        <f>_xlfn.XLOOKUP(B30,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="34">
+        <f t="shared" si="1"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="1">
+        <v>25010901032</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="20">
+        <f>_xlfn.XLOOKUP(B31,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E31" s="33">
+        <f>_xlfn.XLOOKUP(B31,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.666666666666667</v>
+      </c>
+      <c r="F31" s="20">
+        <f>_xlfn.XLOOKUP(B31,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="34">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="1">
+        <v>25010901033</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="20">
+        <f>_xlfn.XLOOKUP(B32,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>6</v>
+      </c>
+      <c r="E32" s="33">
+        <f>_xlfn.XLOOKUP(B32,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F32" s="20">
+        <f>_xlfn.XLOOKUP(B32,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="34">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="1">
+        <v>25010901034</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="20">
+        <f>_xlfn.XLOOKUP(B33,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E33" s="33">
+        <f>_xlfn.XLOOKUP(B33,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.666666666666667</v>
+      </c>
+      <c r="F33" s="20">
+        <f>_xlfn.XLOOKUP(B33,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="34">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="1">
+        <v>25010901035</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="20">
+        <f>_xlfn.XLOOKUP(B34,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E34" s="33">
+        <f>_xlfn.XLOOKUP(B34,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.833333333333333</v>
+      </c>
+      <c r="F34" s="20">
+        <f>_xlfn.XLOOKUP(B34,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="34">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="1">
+        <v>25010901036</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="20">
+        <f>_xlfn.XLOOKUP(B35,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E35" s="33">
+        <f>_xlfn.XLOOKUP(B35,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>3.4166666666666665</v>
+      </c>
+      <c r="F35" s="20">
+        <f>_xlfn.XLOOKUP(B35,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="34">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="1">
+        <v>25010901037</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="20">
+        <f>_xlfn.XLOOKUP(B36,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>6</v>
+      </c>
+      <c r="E36" s="33">
+        <f>_xlfn.XLOOKUP(B36,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F36" s="20">
+        <f>_xlfn.XLOOKUP(B36,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="34">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="1">
+        <v>25010901038</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="20">
+        <f>_xlfn.XLOOKUP(B37,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E37" s="33">
+        <f>_xlfn.XLOOKUP(B37,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="F37" s="20">
+        <f>_xlfn.XLOOKUP(B37,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="34">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="1">
+        <v>25010901039</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="20">
+        <f>_xlfn.XLOOKUP(B38,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="33">
+        <f>_xlfn.XLOOKUP(B38,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="20">
+        <f>_xlfn.XLOOKUP(B38,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="1">
+        <v>24010901023</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="20">
+        <f>_xlfn.XLOOKUP(B39,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="33">
+        <f>_xlfn.XLOOKUP(B39,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>3.1666666666666665</v>
+      </c>
+      <c r="F39" s="20">
+        <f>_xlfn.XLOOKUP(B39,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="34">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="1">
+        <v>24010901033</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="20">
+        <f>_xlfn.XLOOKUP(B40,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
+        <v>3</v>
+      </c>
+      <c r="E40" s="33">
+        <f>_xlfn.XLOOKUP(B40,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="F40" s="20">
+        <f>_xlfn.XLOOKUP(B40,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="34">
+        <f t="shared" si="1"/>
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:D3" xr:uid="{2CB2915B-7E74-40B0-9D48-A1940F1D0007}"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="55" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DCE 2-1/Regular Assessment DCE 2-1.xlsx
+++ b/DCE 2-1/Regular Assessment DCE 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\DCE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8E4587-AA46-4B23-9A7D-16C11E0A4DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9957F72C-F00E-4753-A5A6-4C6896797001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,10 @@
     <sheet name="Assignment" sheetId="8" r:id="rId2"/>
     <sheet name="Class Test" sheetId="9" r:id="rId3"/>
     <sheet name="Eval." sheetId="10" r:id="rId4"/>
+    <sheet name="Seat Plan" sheetId="11" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assignment!$A$3:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assignment!$A$3:$H$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Class Test'!$A$3:$D$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DCE 2-1 Attendance'!$A$3:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Eval.!$A$3:$D$3</definedName>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="106">
   <si>
     <t>SL</t>
   </si>
@@ -232,24 +233,12 @@
     <t>Assignment 2</t>
   </si>
   <si>
-    <t>Comments on 1st Assignemnt</t>
-  </si>
-  <si>
     <t>Not Submitted</t>
   </si>
   <si>
-    <t>Comments on 2nd Assignemnt</t>
-  </si>
-  <si>
-    <t>Comments on 3rd Assignemnt</t>
-  </si>
-  <si>
     <t>Drew 1 Figure</t>
   </si>
   <si>
-    <t>Omit some actions</t>
-  </si>
-  <si>
     <t>NOAS</t>
   </si>
   <si>
@@ -266,6 +255,135 @@
   </si>
   <si>
     <t>BOEV</t>
+  </si>
+  <si>
+    <t>Drew 1 Figure &amp; Omitted some action</t>
+  </si>
+  <si>
+    <t>Omitted some actions</t>
+  </si>
+  <si>
+    <t>Comments on 1st Assignment</t>
+  </si>
+  <si>
+    <t>Comments on 2nd Assignment</t>
+  </si>
+  <si>
+    <t>Comments on 3rd Assignment</t>
+  </si>
+  <si>
+    <t>ID 1</t>
+  </si>
+  <si>
+    <t>ID 2</t>
+  </si>
+  <si>
+    <t>ID 3</t>
+  </si>
+  <si>
+    <t>ID 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID 5 </t>
+  </si>
+  <si>
+    <t>ID 7</t>
+  </si>
+  <si>
+    <t>ID 9</t>
+  </si>
+  <si>
+    <t>ID 10</t>
+  </si>
+  <si>
+    <t>ID 11</t>
+  </si>
+  <si>
+    <t>ID 22</t>
+  </si>
+  <si>
+    <t>ID 33</t>
+  </si>
+  <si>
+    <t>ID 12</t>
+  </si>
+  <si>
+    <t>ID 13</t>
+  </si>
+  <si>
+    <t>ID 14</t>
+  </si>
+  <si>
+    <t>ID 15</t>
+  </si>
+  <si>
+    <t>ID 17</t>
+  </si>
+  <si>
+    <t>ID 19</t>
+  </si>
+  <si>
+    <t>ID 18</t>
+  </si>
+  <si>
+    <t>ID 20</t>
+  </si>
+  <si>
+    <t>ID 21</t>
+  </si>
+  <si>
+    <t>ID 23</t>
+  </si>
+  <si>
+    <t>ID 24</t>
+  </si>
+  <si>
+    <t>ID 25</t>
+  </si>
+  <si>
+    <t>ID 26</t>
+  </si>
+  <si>
+    <t>ID 27</t>
+  </si>
+  <si>
+    <t>ID 29</t>
+  </si>
+  <si>
+    <t>ID 30</t>
+  </si>
+  <si>
+    <t>ID 31</t>
+  </si>
+  <si>
+    <t>ID 32</t>
+  </si>
+  <si>
+    <t>ID 34</t>
+  </si>
+  <si>
+    <t>ID 35</t>
+  </si>
+  <si>
+    <t>ID 36</t>
+  </si>
+  <si>
+    <t>ID 37</t>
+  </si>
+  <si>
+    <t>ID 38</t>
+  </si>
+  <si>
+    <t>ID 39</t>
+  </si>
+  <si>
+    <t>ID R23</t>
+  </si>
+  <si>
+    <t>ID R33</t>
+  </si>
+  <si>
+    <t>SEAT PLAN DCE 51</t>
   </si>
 </sst>
 </file>
@@ -323,7 +441,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -407,6 +525,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDD0CF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -473,7 +597,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -553,6 +677,18 @@
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -571,10 +707,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -665,6 +798,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFDD0CF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -962,10 +1100,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="27"/>
+      <c r="B1" s="31"/>
       <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
@@ -3294,15 +3432,16 @@
     <col min="7" max="7" width="11.44140625" style="7" customWidth="1"/>
     <col min="8" max="8" width="11.44140625" style="24" customWidth="1"/>
     <col min="9" max="9" width="25.44140625" style="7" customWidth="1"/>
-    <col min="10" max="11" width="27.77734375" style="7" customWidth="1"/>
+    <col min="10" max="10" width="37.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.77734375" style="7" customWidth="1"/>
     <col min="12" max="16384" width="20.77734375" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="27"/>
+      <c r="B1" s="31"/>
       <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
@@ -3315,18 +3454,18 @@
       <c r="F1" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="30" t="s">
-        <v>58</v>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="K1" s="34" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -3338,7 +3477,7 @@
         <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>50</v>
@@ -3349,11 +3488,11 @@
       <c r="F2" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
     </row>
     <row r="3" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -3381,9 +3520,9 @@
       <c r="H3" s="22">
         <v>7.5</v>
       </c>
-      <c r="I3" s="29"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
@@ -3440,11 +3579,11 @@
         <f t="shared" ref="H5:H8" si="2">G5/3</f>
         <v>2.3333333333333335</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>59</v>
+      <c r="I5" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>63</v>
       </c>
       <c r="K5" s="1"/>
     </row>
@@ -3504,8 +3643,8 @@
         <f t="shared" si="2"/>
         <v>3.4166666666666665</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>59</v>
+      <c r="I7" s="29" t="s">
+        <v>56</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -3532,11 +3671,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>56</v>
+      <c r="I8" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>55</v>
       </c>
       <c r="K8" s="1"/>
     </row>
@@ -3592,11 +3731,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>56</v>
+      <c r="I10" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" s="30" t="s">
+        <v>55</v>
       </c>
       <c r="K10" s="1"/>
     </row>
@@ -3746,8 +3885,8 @@
         <f t="shared" si="3"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>60</v>
+      <c r="I15" s="29" t="s">
+        <v>64</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -3808,16 +3947,16 @@
         <f t="shared" si="3"/>
         <v>2.9166666666666665</v>
       </c>
-      <c r="I17" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>59</v>
+      <c r="I17" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="J17" s="29" t="s">
+        <v>63</v>
       </c>
       <c r="K17" s="1"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
+      <c r="A18" s="1">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
@@ -3903,7 +4042,9 @@
         <v>3.8333333333333335</v>
       </c>
       <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
+      <c r="J20" s="29" t="s">
+        <v>64</v>
+      </c>
       <c r="K20" s="1"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -3961,8 +4102,8 @@
         <v>2.1666666666666665</v>
       </c>
       <c r="I22" s="1"/>
-      <c r="J22" s="1" t="s">
-        <v>56</v>
+      <c r="J22" s="30" t="s">
+        <v>55</v>
       </c>
       <c r="K22" s="1"/>
     </row>
@@ -4053,8 +4194,8 @@
         <v>3.1666666666666665</v>
       </c>
       <c r="I25" s="1"/>
-      <c r="J25" s="1" t="s">
-        <v>59</v>
+      <c r="J25" s="29" t="s">
+        <v>63</v>
       </c>
       <c r="K25" s="1"/>
     </row>
@@ -4119,7 +4260,7 @@
       <c r="K27" s="1"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="10">
+      <c r="A28" s="1">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
@@ -4354,8 +4495,8 @@
         <f t="shared" si="3"/>
         <v>3.4166666666666665</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>59</v>
+      <c r="I35" s="29" t="s">
+        <v>56</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -4442,11 +4583,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>56</v>
+      <c r="I38" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="J38" s="30" t="s">
+        <v>55</v>
       </c>
       <c r="K38" s="1"/>
     </row>
@@ -4477,8 +4618,8 @@
         <v>3.1666666666666665</v>
       </c>
       <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
-        <v>59</v>
+      <c r="J39" s="29" t="s">
+        <v>63</v>
       </c>
       <c r="K39" s="1"/>
     </row>
@@ -4509,13 +4650,13 @@
         <v>3.3333333333333335</v>
       </c>
       <c r="I40" s="1"/>
-      <c r="J40" s="1" t="s">
-        <v>59</v>
+      <c r="J40" s="29" t="s">
+        <v>63</v>
       </c>
       <c r="K40" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H3" xr:uid="{2CB2915B-7E74-40B0-9D48-A1940F1D0007}"/>
+  <autoFilter ref="A3:H40" xr:uid="{2CB2915B-7E74-40B0-9D48-A1940F1D0007}"/>
   <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="G1:H2"/>
@@ -4525,7 +4666,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="55" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="53" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4545,10 +4686,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="27"/>
+      <c r="B1" s="31"/>
       <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
@@ -4563,10 +4704,10 @@
         <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.3">
@@ -5093,10 +5234,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="27"/>
+      <c r="B1" s="31"/>
       <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
@@ -5114,16 +5255,16 @@
         <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>49</v>
@@ -5167,7 +5308,7 @@
         <f>_xlfn.XLOOKUP(B4,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>6</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="27">
         <f>_xlfn.XLOOKUP(B4,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.166666666666667</v>
       </c>
@@ -5175,7 +5316,7 @@
         <f>_xlfn.XLOOKUP(B4,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="34">
+      <c r="G4" s="28">
         <f>CEILING(SUM(D4:F4),0.5)</f>
         <v>10.5</v>
       </c>
@@ -5195,7 +5336,7 @@
         <f>_xlfn.XLOOKUP(B5,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>6</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="27">
         <f>_xlfn.XLOOKUP(B5,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>2.3333333333333335</v>
       </c>
@@ -5203,7 +5344,7 @@
         <f>_xlfn.XLOOKUP(B5,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="34">
+      <c r="G5" s="28">
         <f t="shared" ref="G5:G40" si="1">CEILING(SUM(D5:F5),0.5)</f>
         <v>8.5</v>
       </c>
@@ -5223,7 +5364,7 @@
         <f>_xlfn.XLOOKUP(B6,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="27">
         <f>_xlfn.XLOOKUP(B6,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4</v>
       </c>
@@ -5231,7 +5372,7 @@
         <f>_xlfn.XLOOKUP(B6,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="28">
         <f t="shared" si="1"/>
         <v>11.5</v>
       </c>
@@ -5251,7 +5392,7 @@
         <f>_xlfn.XLOOKUP(B7,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>6</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="27">
         <f>_xlfn.XLOOKUP(B7,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>3.4166666666666665</v>
       </c>
@@ -5259,7 +5400,7 @@
         <f>_xlfn.XLOOKUP(B7,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="34">
+      <c r="G7" s="28">
         <f t="shared" si="1"/>
         <v>9.5</v>
       </c>
@@ -5279,7 +5420,7 @@
         <f>_xlfn.XLOOKUP(B8,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="27">
         <f>_xlfn.XLOOKUP(B8,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>0</v>
       </c>
@@ -5287,7 +5428,7 @@
         <f>_xlfn.XLOOKUP(B8,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="34">
+      <c r="G8" s="28">
         <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
@@ -5307,7 +5448,7 @@
         <f>_xlfn.XLOOKUP(B9,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>4.5</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="27">
         <f>_xlfn.XLOOKUP(B9,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.833333333333333</v>
       </c>
@@ -5315,7 +5456,7 @@
         <f>_xlfn.XLOOKUP(B9,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="28">
         <f t="shared" si="1"/>
         <v>9.5</v>
       </c>
@@ -5335,7 +5476,7 @@
         <f>_xlfn.XLOOKUP(B10,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="27">
         <f>_xlfn.XLOOKUP(B10,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>0</v>
       </c>
@@ -5343,7 +5484,7 @@
         <f>_xlfn.XLOOKUP(B10,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5363,7 +5504,7 @@
         <f>_xlfn.XLOOKUP(B11,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>6</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="27">
         <f>_xlfn.XLOOKUP(B11,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.5</v>
       </c>
@@ -5371,7 +5512,7 @@
         <f>_xlfn.XLOOKUP(B11,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="28">
         <f t="shared" si="1"/>
         <v>10.5</v>
       </c>
@@ -5391,7 +5532,7 @@
         <f>_xlfn.XLOOKUP(B12,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="27">
         <f>_xlfn.XLOOKUP(B12,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.5</v>
       </c>
@@ -5399,7 +5540,7 @@
         <f>_xlfn.XLOOKUP(B12,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="28">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -5419,7 +5560,7 @@
         <f>_xlfn.XLOOKUP(B13,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="27">
         <f>_xlfn.XLOOKUP(B13,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.166666666666667</v>
       </c>
@@ -5427,7 +5568,7 @@
         <f>_xlfn.XLOOKUP(B13,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="28">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -5447,7 +5588,7 @@
         <f>_xlfn.XLOOKUP(B14,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="27">
         <f>_xlfn.XLOOKUP(B14,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.333333333333333</v>
       </c>
@@ -5455,7 +5596,7 @@
         <f>_xlfn.XLOOKUP(B14,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="28">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -5475,7 +5616,7 @@
         <f>_xlfn.XLOOKUP(B15,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="27">
         <f>_xlfn.XLOOKUP(B15,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>3.6666666666666665</v>
       </c>
@@ -5483,7 +5624,7 @@
         <f>_xlfn.XLOOKUP(B15,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="28">
         <f t="shared" si="1"/>
         <v>11.5</v>
       </c>
@@ -5503,7 +5644,7 @@
         <f>_xlfn.XLOOKUP(B16,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="27">
         <f>_xlfn.XLOOKUP(B16,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>5</v>
       </c>
@@ -5511,7 +5652,7 @@
         <f>_xlfn.XLOOKUP(B16,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="28">
         <f t="shared" si="1"/>
         <v>12.5</v>
       </c>
@@ -5531,7 +5672,7 @@
         <f>_xlfn.XLOOKUP(B17,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>6</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="27">
         <f>_xlfn.XLOOKUP(B17,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>2.9166666666666665</v>
       </c>
@@ -5539,7 +5680,7 @@
         <f>_xlfn.XLOOKUP(B17,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="28">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -5559,7 +5700,7 @@
         <f>_xlfn.XLOOKUP(B18,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="27">
         <f>_xlfn.XLOOKUP(B18,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.166666666666667</v>
       </c>
@@ -5567,7 +5708,7 @@
         <f>_xlfn.XLOOKUP(B18,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="28">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -5587,7 +5728,7 @@
         <f>_xlfn.XLOOKUP(B19,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="27">
         <f>_xlfn.XLOOKUP(B19,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.333333333333333</v>
       </c>
@@ -5595,7 +5736,7 @@
         <f>_xlfn.XLOOKUP(B19,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="28">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -5615,7 +5756,7 @@
         <f>_xlfn.XLOOKUP(B20,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="27">
         <f>_xlfn.XLOOKUP(B20,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>3.8333333333333335</v>
       </c>
@@ -5623,7 +5764,7 @@
         <f>_xlfn.XLOOKUP(B20,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="28">
         <f t="shared" si="1"/>
         <v>11.5</v>
       </c>
@@ -5643,7 +5784,7 @@
         <f>_xlfn.XLOOKUP(B21,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>6</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="27">
         <f>_xlfn.XLOOKUP(B21,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.333333333333333</v>
       </c>
@@ -5651,7 +5792,7 @@
         <f>_xlfn.XLOOKUP(B21,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="28">
         <f t="shared" si="1"/>
         <v>10.5</v>
       </c>
@@ -5671,7 +5812,7 @@
         <f>_xlfn.XLOOKUP(B22,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="27">
         <f>_xlfn.XLOOKUP(B22,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>2.1666666666666665</v>
       </c>
@@ -5679,7 +5820,7 @@
         <f>_xlfn.XLOOKUP(B22,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="28">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -5699,7 +5840,7 @@
         <f>_xlfn.XLOOKUP(B23,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="27">
         <f>_xlfn.XLOOKUP(B23,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.666666666666667</v>
       </c>
@@ -5707,7 +5848,7 @@
         <f>_xlfn.XLOOKUP(B23,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="28">
         <f t="shared" si="1"/>
         <v>12.5</v>
       </c>
@@ -5727,7 +5868,7 @@
         <f>_xlfn.XLOOKUP(B24,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>6</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="27">
         <f>_xlfn.XLOOKUP(B24,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.333333333333333</v>
       </c>
@@ -5735,7 +5876,7 @@
         <f>_xlfn.XLOOKUP(B24,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="28">
         <f t="shared" si="1"/>
         <v>10.5</v>
       </c>
@@ -5755,7 +5896,7 @@
         <f>_xlfn.XLOOKUP(B25,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>6</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="27">
         <f>_xlfn.XLOOKUP(B25,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>3.1666666666666665</v>
       </c>
@@ -5763,7 +5904,7 @@
         <f>_xlfn.XLOOKUP(B25,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="28">
         <f t="shared" si="1"/>
         <v>9.5</v>
       </c>
@@ -5783,7 +5924,7 @@
         <f>_xlfn.XLOOKUP(B26,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E26" s="33">
+      <c r="E26" s="27">
         <f>_xlfn.XLOOKUP(B26,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.833333333333333</v>
       </c>
@@ -5791,7 +5932,7 @@
         <f>_xlfn.XLOOKUP(B26,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="28">
         <f t="shared" si="1"/>
         <v>12.5</v>
       </c>
@@ -5811,7 +5952,7 @@
         <f>_xlfn.XLOOKUP(B27,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>4.5</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="27">
         <f>_xlfn.XLOOKUP(B27,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4</v>
       </c>
@@ -5819,7 +5960,7 @@
         <f>_xlfn.XLOOKUP(B27,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="28">
         <f t="shared" si="1"/>
         <v>8.5</v>
       </c>
@@ -5839,7 +5980,7 @@
         <f>_xlfn.XLOOKUP(B28,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="27">
         <f>_xlfn.XLOOKUP(B28,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.666666666666667</v>
       </c>
@@ -5847,7 +5988,7 @@
         <f>_xlfn.XLOOKUP(B28,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="28">
         <f t="shared" si="1"/>
         <v>12.5</v>
       </c>
@@ -5867,7 +6008,7 @@
         <f>_xlfn.XLOOKUP(B29,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="27">
         <f>_xlfn.XLOOKUP(B29,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.666666666666667</v>
       </c>
@@ -5875,7 +6016,7 @@
         <f>_xlfn.XLOOKUP(B29,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G29" s="34">
+      <c r="G29" s="28">
         <f t="shared" si="1"/>
         <v>12.5</v>
       </c>
@@ -5895,7 +6036,7 @@
         <f>_xlfn.XLOOKUP(B30,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>4.5</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="27">
         <f>_xlfn.XLOOKUP(B30,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.666666666666667</v>
       </c>
@@ -5903,7 +6044,7 @@
         <f>_xlfn.XLOOKUP(B30,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="28">
         <f t="shared" si="1"/>
         <v>9.5</v>
       </c>
@@ -5923,7 +6064,7 @@
         <f>_xlfn.XLOOKUP(B31,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="27">
         <f>_xlfn.XLOOKUP(B31,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.666666666666667</v>
       </c>
@@ -5931,7 +6072,7 @@
         <f>_xlfn.XLOOKUP(B31,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="28">
         <f t="shared" si="1"/>
         <v>12.5</v>
       </c>
@@ -5951,7 +6092,7 @@
         <f>_xlfn.XLOOKUP(B32,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>6</v>
       </c>
-      <c r="E32" s="33">
+      <c r="E32" s="27">
         <f>_xlfn.XLOOKUP(B32,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.5</v>
       </c>
@@ -5959,7 +6100,7 @@
         <f>_xlfn.XLOOKUP(B32,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="28">
         <f t="shared" si="1"/>
         <v>10.5</v>
       </c>
@@ -5979,7 +6120,7 @@
         <f>_xlfn.XLOOKUP(B33,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="27">
         <f>_xlfn.XLOOKUP(B33,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.666666666666667</v>
       </c>
@@ -5987,7 +6128,7 @@
         <f>_xlfn.XLOOKUP(B33,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="28">
         <f t="shared" si="1"/>
         <v>12.5</v>
       </c>
@@ -6007,7 +6148,7 @@
         <f>_xlfn.XLOOKUP(B34,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="27">
         <f>_xlfn.XLOOKUP(B34,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.833333333333333</v>
       </c>
@@ -6015,7 +6156,7 @@
         <f>_xlfn.XLOOKUP(B34,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="28">
         <f t="shared" si="1"/>
         <v>12.5</v>
       </c>
@@ -6035,7 +6176,7 @@
         <f>_xlfn.XLOOKUP(B35,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="27">
         <f>_xlfn.XLOOKUP(B35,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>3.4166666666666665</v>
       </c>
@@ -6043,7 +6184,7 @@
         <f>_xlfn.XLOOKUP(B35,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="28">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
@@ -6063,7 +6204,7 @@
         <f>_xlfn.XLOOKUP(B36,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>6</v>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="27">
         <f>_xlfn.XLOOKUP(B36,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.5</v>
       </c>
@@ -6071,7 +6212,7 @@
         <f>_xlfn.XLOOKUP(B36,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="28">
         <f t="shared" si="1"/>
         <v>10.5</v>
       </c>
@@ -6091,7 +6232,7 @@
         <f>_xlfn.XLOOKUP(B37,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>7.5</v>
       </c>
-      <c r="E37" s="33">
+      <c r="E37" s="27">
         <f>_xlfn.XLOOKUP(B37,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>4.333333333333333</v>
       </c>
@@ -6099,7 +6240,7 @@
         <f>_xlfn.XLOOKUP(B37,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G37" s="34">
+      <c r="G37" s="28">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -6119,7 +6260,7 @@
         <f>_xlfn.XLOOKUP(B38,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>0</v>
       </c>
-      <c r="E38" s="33">
+      <c r="E38" s="27">
         <f>_xlfn.XLOOKUP(B38,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>0</v>
       </c>
@@ -6127,7 +6268,7 @@
         <f>_xlfn.XLOOKUP(B38,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G38" s="34">
+      <c r="G38" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6147,7 +6288,7 @@
         <f>_xlfn.XLOOKUP(B39,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>0</v>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="27">
         <f>_xlfn.XLOOKUP(B39,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>3.1666666666666665</v>
       </c>
@@ -6155,7 +6296,7 @@
         <f>_xlfn.XLOOKUP(B39,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="28">
         <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
@@ -6175,7 +6316,7 @@
         <f>_xlfn.XLOOKUP(B40,'DCE 2-1 Attendance'!$B$4:$B$40,'DCE 2-1 Attendance'!$E$4:$E$40)</f>
         <v>3</v>
       </c>
-      <c r="E40" s="33">
+      <c r="E40" s="27">
         <f>_xlfn.XLOOKUP(B40,Assignment!$B$4:$B$40,Assignment!$H$4:$H$40)</f>
         <v>3.3333333333333335</v>
       </c>
@@ -6183,7 +6324,7 @@
         <f>_xlfn.XLOOKUP(B40,'Class Test'!$B$4:$B$40,'Class Test'!$D$4:$D$40)</f>
         <v>0</v>
       </c>
-      <c r="G40" s="34">
+      <c r="G40" s="28">
         <f t="shared" si="1"/>
         <v>6.5</v>
       </c>
@@ -6197,4 +6338,159 @@
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7BC1AF-A25E-405B-A2DF-B3480BC80B63}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="23.109375" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="23.109375" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+    </row>
+    <row r="2" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>